--- a/docs/bieroverzicht.xlsx
+++ b/docs/bieroverzicht.xlsx
@@ -2699,7 +2699,11 @@
           <t>https://debiersalon.nl/products/moersleutel-craft-brewery-barcode-silver-aquamarine</t>
         </is>
       </c>
-      <c r="K43" s="2" t="n"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>al gehad</t>
+        </is>
+      </c>
       <c r="L43" s="7" t="n">
         <v>70.8</v>
       </c>
@@ -7049,12 +7053,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Drekker Brewing Company</t>
-        </is>
-      </c>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>Slang Du Jour - Key Lime Pie - 2026</t>
+          <t>Le Ketch</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Dock 131 - Citra &amp; Riwaka</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
@@ -7062,34 +7066,34 @@
       </c>
       <c r="D130" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>Sour - Smoothie / Pastry</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="G130" s="4" t="n">
-        <v>4.13</v>
+        <v>4.18</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>498</v>
+        <v>223</v>
       </c>
       <c r="I130" s="5" t="n">
-        <v>11.49</v>
+        <v>8.02</v>
       </c>
       <c r="J130" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/drekker-brewing-company-slang-du-jour-key-lime-pie-2026</t>
+          <t>https://debiersalon.nl/products/le-ketch-dock-131-citra-riwaka</t>
         </is>
       </c>
       <c r="K130" s="2" t="n"/>
       <c r="L130" s="7" t="n">
-        <v>57.8</v>
+        <v>58</v>
       </c>
       <c r="M130" s="5" t="n"/>
       <c r="N130" s="5" t="n"/>
@@ -7099,16 +7103,16 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Imprint Beer Co.</t>
+          <t>Drekker Brewing Company</t>
         </is>
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>Bourbon Barrel Aged Pecan Like A Bomb</t>
+          <t>Slang Du Jour - Key Lime Pie - 2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
-        <v>35.5</v>
+        <v>47.3</v>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
@@ -7116,30 +7120,30 @@
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>13.5</v>
+        <v>6.2</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double Pastry</t>
+          <t>Sour - Smoothie / Pastry</t>
         </is>
       </c>
       <c r="G131" s="4" t="n">
-        <v>4.27</v>
+        <v>4.13</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>547</v>
+        <v>498</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>14.69</v>
+        <v>11.49</v>
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/imprint-beer-co-bourbon-barrel-aged-pecan-like-a-bomb</t>
+          <t>https://debiersalon.nl/products/drekker-brewing-company-slang-du-jour-key-lime-pie-2026</t>
         </is>
       </c>
       <c r="K131" s="2" t="n"/>
       <c r="L131" s="7" t="n">
-        <v>57.7</v>
+        <v>57.8</v>
       </c>
       <c r="M131" s="5" t="n"/>
       <c r="N131" s="5" t="n"/>
@@ -7149,24 +7153,24 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Brouwerij Kees</t>
+          <t>Imprint Beer Co.</t>
         </is>
       </c>
       <c r="B132" s="3" t="inlineStr">
         <is>
-          <t>Barrel Project 2026 Experience Editie</t>
+          <t>Bourbon Barrel Aged Pecan Like A Bomb</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
-        <v>75</v>
+        <v>35.5</v>
       </c>
       <c r="D132" s="2" t="inlineStr">
         <is>
-          <t>Nederland</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>12.2</v>
+        <v>13.5</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
@@ -7174,22 +7178,22 @@
         </is>
       </c>
       <c r="G132" s="4" t="n">
-        <v>4.03</v>
+        <v>4.27</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>254</v>
+        <v>547</v>
       </c>
       <c r="I132" s="5" t="n">
-        <v>12.99</v>
+        <v>14.69</v>
       </c>
       <c r="J132" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/brouwerij-kees-barrel-project-2026-experience-editie</t>
+          <t>https://debiersalon.nl/products/imprint-beer-co-bourbon-barrel-aged-pecan-like-a-bomb</t>
         </is>
       </c>
       <c r="K132" s="2" t="n"/>
       <c r="L132" s="7" t="n">
-        <v>57.6</v>
+        <v>57.7</v>
       </c>
       <c r="M132" s="5" t="n"/>
       <c r="N132" s="5" t="n"/>
@@ -7199,24 +7203,24 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Blackout Brewing</t>
+          <t>Brouwerij Kees</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>Bless This Mess Vol 4</t>
+          <t>Barrel Project 2026 Experience Editie</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Roemenië</t>
+          <t>Nederland</t>
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7224,103 +7228,103 @@
         </is>
       </c>
       <c r="G133" s="4" t="n">
-        <v>4.21</v>
+        <v>4.03</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>38</v>
+        <v>254</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>11.49</v>
+        <v>12.99</v>
       </c>
       <c r="J133" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/blackout-brewing-bless-this-mess-vol-4</t>
+          <t>https://debiersalon.nl/products/brouwerij-kees-barrel-project-2026-experience-editie</t>
         </is>
       </c>
       <c r="K133" s="2" t="n"/>
       <c r="L133" s="7" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="M133" s="5" t="n">
-        <v>12.99</v>
-      </c>
+        <v>57.6</v>
+      </c>
+      <c r="M133" s="5" t="n"/>
       <c r="N133" s="5" t="n"/>
       <c r="O133" s="5" t="n"/>
-      <c r="P133" s="5" t="n">
-        <v>12.75</v>
-      </c>
+      <c r="P133" s="5" t="n"/>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Verdant Brewing Co</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>Under the Same Sky</t>
+          <t>Blackout Brewing</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>Bless This Mess Vol 4</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D134" s="2" t="inlineStr">
         <is>
-          <t>Engeland</t>
+          <t>Roemenië</t>
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>Stout - Imperial / Double Pastry</t>
         </is>
       </c>
       <c r="G134" s="4" t="n">
-        <v>4.19</v>
+        <v>4.21</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>6534</v>
+        <v>38</v>
       </c>
       <c r="I134" s="5" t="n">
-        <v>9.69</v>
+        <v>11.49</v>
       </c>
       <c r="J134" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/verdant-brewing-co-under-the-same-sky</t>
+          <t>https://debiersalon.nl/products/blackout-brewing-bless-this-mess-vol-4</t>
         </is>
       </c>
       <c r="K134" s="2" t="n"/>
       <c r="L134" s="7" t="n">
-        <v>57.3</v>
-      </c>
-      <c r="M134" s="5" t="n"/>
+        <v>57.5</v>
+      </c>
+      <c r="M134" s="5" t="n">
+        <v>12.99</v>
+      </c>
       <c r="N134" s="5" t="n"/>
       <c r="O134" s="5" t="n"/>
-      <c r="P134" s="5" t="n"/>
+      <c r="P134" s="5" t="n">
+        <v>12.75</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>WeldWerks Brewing Co.</t>
+          <t>Verdant Brewing Co</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>The Best Citra</t>
+          <t>Under the Same Sky</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
-        <v>47.3</v>
+        <v>44</v>
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Engeland</t>
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7328,22 +7332,22 @@
         </is>
       </c>
       <c r="G135" s="4" t="n">
-        <v>4.18</v>
+        <v>4.19</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>4965</v>
+        <v>6534</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>9.99</v>
+        <v>9.69</v>
       </c>
       <c r="J135" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/weldwerks-brewing-co-the-best-citra</t>
+          <t>https://debiersalon.nl/products/verdant-brewing-co-under-the-same-sky</t>
         </is>
       </c>
       <c r="K135" s="2" t="n"/>
       <c r="L135" s="7" t="n">
-        <v>57.2</v>
+        <v>57.3</v>
       </c>
       <c r="M135" s="5" t="n"/>
       <c r="N135" s="5" t="n"/>
@@ -7353,12 +7357,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Perennial Artisan Ales</t>
+          <t>WeldWerks Brewing Co.</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Sump (2025)</t>
+          <t>The Best Citra</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
@@ -7370,30 +7374,30 @@
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>11.5</v>
+        <v>8.5</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double Coffee</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="G136" s="4" t="n">
-        <v>4.21</v>
+        <v>4.18</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>1221</v>
+        <v>4965</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>12.49</v>
+        <v>9.99</v>
       </c>
       <c r="J136" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/perennial-artisan-ales-sump-2026</t>
+          <t>https://debiersalon.nl/products/weldwerks-brewing-co-the-best-citra</t>
         </is>
       </c>
       <c r="K136" s="2" t="n"/>
       <c r="L136" s="7" t="n">
-        <v>57</v>
+        <v>57.2</v>
       </c>
       <c r="M136" s="5" t="n"/>
       <c r="N136" s="5" t="n"/>
@@ -7403,47 +7407,47 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>SOMA Beer</t>
+          <t>Perennial Artisan Ales</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Eerie</t>
+          <t>Sump (2025)</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
-        <v>44</v>
+        <v>47.3</v>
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Spanje</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
+          <t>Stout - Imperial / Double Coffee</t>
         </is>
       </c>
       <c r="G137" s="4" t="n">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>65</v>
+        <v>1221</v>
       </c>
       <c r="I137" s="5" t="n">
-        <v>6.89</v>
+        <v>12.49</v>
       </c>
       <c r="J137" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/soma-beer-eerie</t>
+          <t>https://debiersalon.nl/products/perennial-artisan-ales-sump-2026</t>
         </is>
       </c>
       <c r="K137" s="2" t="n"/>
       <c r="L137" s="7" t="n">
-        <v>56.9</v>
+        <v>57</v>
       </c>
       <c r="M137" s="5" t="n"/>
       <c r="N137" s="5" t="n"/>
@@ -7453,42 +7457,42 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Other Half Brewing Co.</t>
+          <t>SOMA Beer</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Raw Concrete (TEST collab)</t>
+          <t>Eerie</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
-        <v>47.3</v>
+        <v>44</v>
       </c>
       <c r="D138" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Spanje</t>
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="G138" s="4" t="n">
         <v>4.17</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>1345</v>
+        <v>65</v>
       </c>
       <c r="I138" s="5" t="n">
-        <v>8.99</v>
+        <v>6.89</v>
       </c>
       <c r="J138" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/other-half-brewing-co-raw-concrete</t>
+          <t>https://debiersalon.nl/products/soma-beer-eerie</t>
         </is>
       </c>
       <c r="K138" s="2" t="n"/>
@@ -7503,12 +7507,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Third Moon Brewing Company</t>
+          <t>Other Half Brewing Co.</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Double Bruiser</t>
+          <t>Raw Concrete (TEST collab)</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
@@ -7516,7 +7520,7 @@
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E139" s="2" t="n">
@@ -7528,17 +7532,17 @@
         </is>
       </c>
       <c r="G139" s="4" t="n">
-        <v>4.26</v>
+        <v>4.17</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>322</v>
+        <v>1345</v>
       </c>
       <c r="I139" s="5" t="n">
-        <v>11.49</v>
+        <v>8.99</v>
       </c>
       <c r="J139" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/third-moon-brewing-company-double-bruiser</t>
+          <t>https://debiersalon.nl/products/other-half-brewing-co-raw-concrete</t>
         </is>
       </c>
       <c r="K139" s="2" t="n"/>
@@ -7553,47 +7557,47 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Lough Gill Brewery</t>
+          <t>Third Moon Brewing Company</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Shamrock Barrel Aged</t>
+          <t>Double Bruiser</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
-        <v>33</v>
+        <v>47.3</v>
       </c>
       <c r="D140" s="2" t="inlineStr">
         <is>
-          <t>Ierland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>14.8</v>
+        <v>8</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double Coffee</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="G140" s="4" t="n">
-        <v>4.17</v>
+        <v>4.26</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>457</v>
+        <v>322</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>7.19</v>
+        <v>11.49</v>
       </c>
       <c r="J140" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/lough-gill-brewery-shamrock-barrel-aged</t>
+          <t>https://debiersalon.nl/products/third-moon-brewing-company-double-bruiser</t>
         </is>
       </c>
       <c r="K140" s="2" t="n"/>
       <c r="L140" s="7" t="n">
-        <v>56.8</v>
+        <v>56.9</v>
       </c>
       <c r="M140" s="5" t="n"/>
       <c r="N140" s="5" t="n"/>
@@ -7603,47 +7607,47 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Finback Brewery</t>
-        </is>
-      </c>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>Backcountry Trail</t>
+          <t>Lough Gill Brewery</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Shamrock Barrel Aged</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
-        <v>47.3</v>
+        <v>33</v>
       </c>
       <c r="D141" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Ierland</t>
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>8</v>
+        <v>14.8</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double</t>
+          <t>Stout - Imperial / Double Coffee</t>
         </is>
       </c>
       <c r="G141" s="4" t="n">
-        <v>4.06</v>
+        <v>4.17</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>508</v>
+        <v>457</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>9.69</v>
+        <v>7.19</v>
       </c>
       <c r="J141" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/finback-brewery-backcountry-trail</t>
+          <t>https://debiersalon.nl/products/lough-gill-brewery-shamrock-barrel-aged</t>
         </is>
       </c>
       <c r="K141" s="2" t="n"/>
       <c r="L141" s="7" t="n">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
       <c r="M141" s="5" t="n"/>
       <c r="N141" s="5" t="n"/>
@@ -7653,12 +7657,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Mortalis Brewing Company</t>
+          <t>Finback Brewery</t>
         </is>
       </c>
       <c r="B142" s="3" t="inlineStr">
         <is>
-          <t>Gemini | Blueberry + Soursop + Coconut</t>
+          <t>Backcountry Trail</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
@@ -7670,34 +7674,32 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Sour - Smoothie / Pastry</t>
+          <t>IPA - Imperial / Double</t>
         </is>
       </c>
       <c r="G142" s="4" t="n">
-        <v>4.15</v>
+        <v>4.06</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>832</v>
+        <v>508</v>
       </c>
       <c r="I142" s="5" t="n">
-        <v>12.79</v>
+        <v>9.69</v>
       </c>
       <c r="J142" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/mortalis-brewing-company-gemini-blueberry-soursop-coconut</t>
+          <t>https://debiersalon.nl/products/finback-brewery-backcountry-trail</t>
         </is>
       </c>
       <c r="K142" s="2" t="n"/>
       <c r="L142" s="7" t="n">
-        <v>56.6</v>
-      </c>
-      <c r="M142" s="5" t="n">
-        <v>13.99</v>
-      </c>
+        <v>56.7</v>
+      </c>
+      <c r="M142" s="5" t="n"/>
       <c r="N142" s="5" t="n"/>
       <c r="O142" s="5" t="n"/>
       <c r="P142" s="5" t="n"/>
@@ -7705,20 +7707,20 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Norm Brewing</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>KIA ORA</t>
+          <t>Mortalis Brewing Company</t>
+        </is>
+      </c>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>Gemini | Blueberry + Soursop + Coconut</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
-        <v>44</v>
+        <v>47.3</v>
       </c>
       <c r="D143" s="2" t="inlineStr">
         <is>
-          <t>België</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E143" s="2" t="n">
@@ -7726,24 +7728,30 @@
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>IPA</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="n"/>
-      <c r="H143" s="2" t="n"/>
+          <t>Sour - Smoothie / Pastry</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>832</v>
+      </c>
       <c r="I143" s="5" t="n">
-        <v>5.99</v>
+        <v>12.79</v>
       </c>
       <c r="J143" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/norm-brewing-kia-ora</t>
+          <t>https://debiersalon.nl/products/mortalis-brewing-company-gemini-blueberry-soursop-coconut</t>
         </is>
       </c>
       <c r="K143" s="2" t="n"/>
       <c r="L143" s="7" t="n">
-        <v>56.5</v>
-      </c>
-      <c r="M143" s="5" t="n"/>
+        <v>56.6</v>
+      </c>
+      <c r="M143" s="5" t="n">
+        <v>13.99</v>
+      </c>
       <c r="N143" s="5" t="n"/>
       <c r="O143" s="5" t="n"/>
       <c r="P143" s="5" t="n"/>
@@ -7751,42 +7759,38 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Badlands Brewing Company</t>
+          <t>Norm Brewing</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Su Su Maru</t>
+          <t>KIA ORA</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
-        <v>47.3</v>
+        <v>44</v>
       </c>
       <c r="D144" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>België</t>
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
           <t>IPA</t>
         </is>
       </c>
-      <c r="G144" s="4" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="H144" s="2" t="n">
-        <v>382</v>
-      </c>
+      <c r="G144" s="2" t="n"/>
+      <c r="H144" s="2" t="n"/>
       <c r="I144" s="5" t="n">
-        <v>8.02</v>
+        <v>5.99</v>
       </c>
       <c r="J144" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/badlands-brewing-company-su-su-maru</t>
+          <t>https://debiersalon.nl/products/norm-brewing-kia-ora</t>
         </is>
       </c>
       <c r="K144" s="2" t="n"/>
@@ -7801,12 +7805,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Flying Monkeys Craft Brewery</t>
+          <t>Badlands Brewing Company</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>The Chocolate Manifesto</t>
+          <t>Su Su Maru</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
@@ -7818,30 +7822,30 @@
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double Milk</t>
+          <t>IPA</t>
         </is>
       </c>
       <c r="G145" s="4" t="n">
-        <v>4.11</v>
+        <v>4.16</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>50204</v>
+        <v>382</v>
       </c>
       <c r="I145" s="5" t="n">
-        <v>7.29</v>
+        <v>8.02</v>
       </c>
       <c r="J145" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/flying-monkeys-craft-brewery-the-chocolate-manifesto</t>
+          <t>https://debiersalon.nl/products/badlands-brewing-company-su-su-maru</t>
         </is>
       </c>
       <c r="K145" s="2" t="n"/>
       <c r="L145" s="7" t="n">
-        <v>56.4</v>
+        <v>56.5</v>
       </c>
       <c r="M145" s="5" t="n"/>
       <c r="N145" s="5" t="n"/>
@@ -7851,12 +7855,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Mortalis Brewing Company</t>
+          <t>Flying Monkeys Craft Brewery</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Persephone</t>
+          <t>The Chocolate Manifesto</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
@@ -7864,34 +7868,34 @@
       </c>
       <c r="D146" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E146" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>Stout - Imperial / Double Milk</t>
         </is>
       </c>
       <c r="G146" s="4" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>2194</v>
+        <v>50204</v>
       </c>
       <c r="I146" s="5" t="n">
-        <v>11.99</v>
+        <v>7.29</v>
       </c>
       <c r="J146" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/mortalis-brewing-company-persephone</t>
+          <t>https://debiersalon.nl/products/flying-monkeys-craft-brewery-the-chocolate-manifesto</t>
         </is>
       </c>
       <c r="K146" s="2" t="n"/>
       <c r="L146" s="7" t="n">
-        <v>56.3</v>
+        <v>56.4</v>
       </c>
       <c r="M146" s="5" t="n"/>
       <c r="N146" s="5" t="n"/>
@@ -7901,12 +7905,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Messorem</t>
+          <t>Mortalis Brewing Company</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Demoliri 0029</t>
+          <t>Persephone</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
@@ -7914,38 +7918,36 @@
       </c>
       <c r="D147" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="G147" s="4" t="n">
-        <v>4.21</v>
+        <v>4.25</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>542</v>
+        <v>2194</v>
       </c>
       <c r="I147" s="5" t="n">
-        <v>10.49</v>
+        <v>11.99</v>
       </c>
       <c r="J147" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/messorem-demoliri-0029</t>
+          <t>https://debiersalon.nl/products/mortalis-brewing-company-persephone</t>
         </is>
       </c>
       <c r="K147" s="2" t="n"/>
       <c r="L147" s="7" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="M147" s="5" t="n">
-        <v>10.99</v>
-      </c>
+        <v>56.3</v>
+      </c>
+      <c r="M147" s="5" t="n"/>
       <c r="N147" s="5" t="n"/>
       <c r="O147" s="5" t="n"/>
       <c r="P147" s="5" t="n"/>
@@ -7953,12 +7955,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Fine Balance Brewing</t>
+          <t>Messorem</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Double Oats &amp; Cream: Select Nelson Sauvin &amp; Citra</t>
+          <t>Demoliri 0029</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
@@ -7970,32 +7972,34 @@
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>8.1</v>
+        <v>7</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="G148" s="4" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>202</v>
+        <v>542</v>
       </c>
       <c r="I148" s="5" t="n">
         <v>10.49</v>
       </c>
       <c r="J148" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/fine-balance-brewing-double-oats-cream-select-nelson-sauvin-citra</t>
+          <t>https://debiersalon.nl/products/messorem-demoliri-0029</t>
         </is>
       </c>
       <c r="K148" s="2" t="n"/>
       <c r="L148" s="7" t="n">
-        <v>56.1</v>
-      </c>
-      <c r="M148" s="5" t="n"/>
+        <v>56.2</v>
+      </c>
+      <c r="M148" s="5" t="n">
+        <v>10.99</v>
+      </c>
       <c r="N148" s="5" t="n"/>
       <c r="O148" s="5" t="n"/>
       <c r="P148" s="5" t="n"/>
@@ -8003,43 +8007,47 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Aspro Brews</t>
+          <t>Fine Balance Brewing</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Raincoat</t>
+          <t>Double Oats &amp; Cream: Select Nelson Sauvin &amp; Citra</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
-        <v>44</v>
+        <v>47.3</v>
       </c>
       <c r="D149" s="2" t="inlineStr">
         <is>
-          <t>Nederland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>6.1</v>
+        <v>8.1</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="n"/>
-      <c r="H149" s="2" t="n"/>
+          <t>IPA - Imperial / Double New England / Hazy</t>
+        </is>
+      </c>
+      <c r="G149" s="4" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>202</v>
+      </c>
       <c r="I149" s="5" t="n">
-        <v>6.19</v>
+        <v>10.49</v>
       </c>
       <c r="J149" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/aspro-brews-raincoat</t>
+          <t>https://debiersalon.nl/products/fine-balance-brewing-double-oats-cream-select-nelson-sauvin-citra</t>
         </is>
       </c>
       <c r="K149" s="2" t="n"/>
       <c r="L149" s="7" t="n">
-        <v>56</v>
+        <v>56.1</v>
       </c>
       <c r="M149" s="5" t="n"/>
       <c r="N149" s="5" t="n"/>
@@ -8049,12 +8057,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Norm Brewing</t>
+          <t>Aspro Brews</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Radiant</t>
+          <t>Raincoat</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
@@ -8062,15 +8070,15 @@
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>België</t>
+          <t>Nederland</t>
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="G150" s="2" t="n"/>
@@ -8080,7 +8088,7 @@
       </c>
       <c r="J150" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/norm-brewing-radiant</t>
+          <t>https://debiersalon.nl/products/aspro-brews-raincoat</t>
         </is>
       </c>
       <c r="K150" s="2" t="n"/>
@@ -8095,42 +8103,38 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Brasserie du Bas-Canada</t>
+          <t>Norm Brewing</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Vas Florarium</t>
+          <t>Radiant</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
-        <v>47.3</v>
+        <v>44</v>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>België</t>
         </is>
       </c>
       <c r="E151" s="2" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
-          <t>IPA</t>
-        </is>
-      </c>
-      <c r="G151" s="4" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="H151" s="2" t="n">
-        <v>464</v>
-      </c>
+          <t>IPA - Imperial / Double New England / Hazy</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="n"/>
+      <c r="H151" s="2" t="n"/>
       <c r="I151" s="5" t="n">
-        <v>7.87</v>
+        <v>6.19</v>
       </c>
       <c r="J151" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/brasserie-du-bas-canada-vas-florarium</t>
+          <t>https://debiersalon.nl/products/norm-brewing-radiant</t>
         </is>
       </c>
       <c r="K151" s="2" t="n"/>
@@ -8145,12 +8149,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Le Ketch</t>
+          <t>Brasserie du Bas-Canada</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Capitaine Fresh - Le Ketch X Sir John</t>
+          <t>Vas Florarium</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
@@ -8162,30 +8166,30 @@
         </is>
       </c>
       <c r="E152" s="2" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>IPA</t>
         </is>
       </c>
       <c r="G152" s="4" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>304</v>
+        <v>464</v>
       </c>
       <c r="I152" s="5" t="n">
-        <v>11.49</v>
+        <v>7.87</v>
       </c>
       <c r="J152" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/le-ketch-capitaine-fresh-le-ketch-x-sir-john</t>
+          <t>https://debiersalon.nl/products/brasserie-du-bas-canada-vas-florarium</t>
         </is>
       </c>
       <c r="K152" s="2" t="n"/>
       <c r="L152" s="7" t="n">
-        <v>55.9</v>
+        <v>56</v>
       </c>
       <c r="M152" s="5" t="n"/>
       <c r="N152" s="5" t="n"/>
@@ -8195,80 +8199,74 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Azvex Brewing Company</t>
+          <t>Le Ketch</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Operation Genome [26.04] - 3 Sons</t>
+          <t>Capitaine Fresh - Le Ketch X Sir John</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
-        <v>44</v>
+        <v>47.3</v>
       </c>
       <c r="D153" s="2" t="inlineStr">
         <is>
-          <t>Engeland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E153" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="G153" s="4" t="n">
-        <v>4.23</v>
+        <v>4.25</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>813</v>
+        <v>304</v>
       </c>
       <c r="I153" s="5" t="n">
-        <v>12.89</v>
+        <v>11.49</v>
       </c>
       <c r="J153" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/azvex-brewing-company-operation-genome-26-04-3-sons</t>
+          <t>https://debiersalon.nl/products/le-ketch-capitaine-fresh-le-ketch-x-sir-john</t>
         </is>
       </c>
       <c r="K153" s="2" t="n"/>
       <c r="L153" s="7" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="M153" s="5" t="n">
-        <v>12.99</v>
-      </c>
+        <v>55.9</v>
+      </c>
+      <c r="M153" s="5" t="n"/>
       <c r="N153" s="5" t="n"/>
-      <c r="O153" s="5" t="n">
-        <v>13.59</v>
-      </c>
-      <c r="P153" s="5" t="n">
-        <v>12.5</v>
-      </c>
+      <c r="O153" s="5" t="n"/>
+      <c r="P153" s="5" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Big Belly Brewing Company</t>
+          <t>Azvex Brewing Company</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>AETHELSTAN - Barrel Aged 2026</t>
+          <t>Operation Genome [26.04] - 3 Sons</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D154" s="2" t="inlineStr">
         <is>
-          <t>Nederland</t>
+          <t>Engeland</t>
         </is>
       </c>
       <c r="E154" s="2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -8276,69 +8274,73 @@
         </is>
       </c>
       <c r="G154" s="4" t="n">
-        <v>4.2</v>
+        <v>4.23</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>343</v>
+        <v>813</v>
       </c>
       <c r="I154" s="5" t="n">
-        <v>8.99</v>
+        <v>12.89</v>
       </c>
       <c r="J154" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/big-belly-brewing-company-aethelstan-barrel-aged-2026</t>
+          <t>https://debiersalon.nl/products/azvex-brewing-company-operation-genome-26-04-3-sons</t>
         </is>
       </c>
       <c r="K154" s="2" t="n"/>
       <c r="L154" s="7" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="M154" s="5" t="n"/>
+        <v>55.8</v>
+      </c>
+      <c r="M154" s="5" t="n">
+        <v>12.99</v>
+      </c>
       <c r="N154" s="5" t="n"/>
-      <c r="O154" s="5" t="n"/>
+      <c r="O154" s="5" t="n">
+        <v>13.59</v>
+      </c>
       <c r="P154" s="5" t="n">
-        <v>9.25</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Hoof Hearted Brewing</t>
+          <t>Big Belly Brewing Company</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>If You Can't Be Good, Be Bald</t>
+          <t>AETHELSTAN - Barrel Aged 2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
-        <v>47.3</v>
+        <v>33</v>
       </c>
       <c r="D155" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Nederland</t>
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>8.5</v>
+        <v>10.5</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>Stout - Imperial / Double</t>
         </is>
       </c>
       <c r="G155" s="4" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>84</v>
+        <v>343</v>
       </c>
       <c r="I155" s="5" t="n">
-        <v>9.99</v>
+        <v>8.99</v>
       </c>
       <c r="J155" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/hoof-hearted-brewing-if-you-cant-be-good-be-bald</t>
+          <t>https://debiersalon.nl/products/big-belly-brewing-company-aethelstan-barrel-aged-2026</t>
         </is>
       </c>
       <c r="K155" s="2" t="n"/>
@@ -8348,47 +8350,49 @@
       <c r="M155" s="5" t="n"/>
       <c r="N155" s="5" t="n"/>
       <c r="O155" s="5" t="n"/>
-      <c r="P155" s="5" t="n"/>
+      <c r="P155" s="5" t="n">
+        <v>9.25</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Low Key Barrel Project</t>
-        </is>
-      </c>
-      <c r="B156" s="3" t="inlineStr">
-        <is>
-          <t>I'M TWO QUARTERS AND A HEART DOWN</t>
+          <t>Hoof Hearted Brewing</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>If You Can't Be Good, Be Bald</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
-        <v>33</v>
+        <v>47.3</v>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>Engeland</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E156" s="2" t="n">
-        <v>10.6</v>
+        <v>8.5</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double Pastry</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="G156" s="4" t="n">
-        <v>4.1</v>
+        <v>4.21</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>896</v>
+        <v>84</v>
       </c>
       <c r="I156" s="5" t="n">
-        <v>7.99</v>
+        <v>9.99</v>
       </c>
       <c r="J156" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/low-key-barrel-project-im-two-quarters-and-a-heart-down</t>
+          <t>https://debiersalon.nl/products/hoof-hearted-brewing-if-you-cant-be-good-be-bald</t>
         </is>
       </c>
       <c r="K156" s="2" t="n"/>
@@ -8403,47 +8407,47 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Stigbergets Bryggeri</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>BIGGER! BOLDER!</t>
+          <t>Low Key Barrel Project</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>I'M TWO QUARTERS AND A HEART DOWN</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Zweden</t>
+          <t>Engeland</t>
         </is>
       </c>
       <c r="E157" s="2" t="n">
-        <v>8.5</v>
+        <v>10.6</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>Stout - Imperial / Double Pastry</t>
         </is>
       </c>
       <c r="G157" s="4" t="n">
-        <v>4.09</v>
+        <v>4.1</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>13082</v>
+        <v>896</v>
       </c>
       <c r="I157" s="5" t="n">
-        <v>6.19</v>
+        <v>7.99</v>
       </c>
       <c r="J157" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/stigbergets-bryggeri-bigger-bolder</t>
+          <t>https://debiersalon.nl/products/low-key-barrel-project-im-two-quarters-and-a-heart-down</t>
         </is>
       </c>
       <c r="K157" s="2" t="n"/>
       <c r="L157" s="7" t="n">
-        <v>55.5</v>
+        <v>55.7</v>
       </c>
       <c r="M157" s="5" t="n"/>
       <c r="N157" s="5" t="n"/>
@@ -8453,47 +8457,47 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Hop Hooligans</t>
+          <t>Stigbergets Bryggeri</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Parasomnia: Rum &amp; Bourbon BA Tonka (2026, Golden Wax)</t>
+          <t>BIGGER! BOLDER!</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
-        <v>37.5</v>
+        <v>44</v>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>Roemenië</t>
+          <t>Zweden</t>
         </is>
       </c>
       <c r="E158" s="2" t="n">
-        <v>17</v>
+        <v>8.5</v>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="G158" s="4" t="n">
-        <v>4.29</v>
+        <v>4.09</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>528</v>
+        <v>13082</v>
       </c>
       <c r="I158" s="5" t="n">
-        <v>13.49</v>
+        <v>6.19</v>
       </c>
       <c r="J158" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/hop-hooligans-parasomnia-rum-bourbon-ba-tonka-2026-golden-wax</t>
+          <t>https://debiersalon.nl/products/stigbergets-bryggeri-bigger-bolder</t>
         </is>
       </c>
       <c r="K158" s="2" t="n"/>
       <c r="L158" s="7" t="n">
-        <v>55.4</v>
+        <v>55.5</v>
       </c>
       <c r="M158" s="5" t="n"/>
       <c r="N158" s="5" t="n"/>
@@ -8503,51 +8507,49 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Brouwerij Verhaeghe</t>
+          <t>Hop Hooligans</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Duchesse Red</t>
+          <t>Parasomnia: Rum &amp; Bourbon BA Tonka (2026, Golden Wax)</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
-        <v>33</v>
+        <v>37.5</v>
       </c>
       <c r="D159" s="2" t="inlineStr">
         <is>
-          <t>België</t>
+          <t>Roemenië</t>
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
-          <t>Sour</t>
+          <t>Stout - Imperial / Double</t>
         </is>
       </c>
       <c r="G159" s="4" t="n">
-        <v>4.05</v>
+        <v>4.29</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>6318</v>
+        <v>528</v>
       </c>
       <c r="I159" s="5" t="n">
-        <v>3.39</v>
+        <v>13.49</v>
       </c>
       <c r="J159" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/brouwerij-verhaeghe-duchesse-red</t>
+          <t>https://debiersalon.nl/products/hop-hooligans-parasomnia-rum-bourbon-ba-tonka-2026-golden-wax</t>
         </is>
       </c>
       <c r="K159" s="2" t="n"/>
       <c r="L159" s="7" t="n">
         <v>55.4</v>
       </c>
-      <c r="M159" s="5" t="n">
-        <v>3.49</v>
-      </c>
+      <c r="M159" s="5" t="n"/>
       <c r="N159" s="5" t="n"/>
       <c r="O159" s="5" t="n"/>
       <c r="P159" s="5" t="n"/>
@@ -8555,146 +8557,148 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Arpus</t>
+          <t>Brouwerij Verhaeghe</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Mango X Pineapple Gose</t>
+          <t>Duchesse Red</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D160" s="2" t="inlineStr">
         <is>
-          <t>Letland</t>
+          <t>België</t>
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
-          <t>Sour - Fruited Gose</t>
+          <t>Sour</t>
         </is>
       </c>
       <c r="G160" s="4" t="n">
-        <v>4.14</v>
+        <v>4.05</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>34</v>
+        <v>6318</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>5.99</v>
+        <v>3.39</v>
       </c>
       <c r="J160" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/arpus-mango-x-pineapple-gose</t>
+          <t>https://debiersalon.nl/products/brouwerij-verhaeghe-duchesse-red</t>
         </is>
       </c>
       <c r="K160" s="2" t="n"/>
       <c r="L160" s="7" t="n">
-        <v>55.1</v>
+        <v>55.4</v>
       </c>
       <c r="M160" s="5" t="n">
-        <v>6.69</v>
-      </c>
-      <c r="N160" s="5" t="n">
-        <v>5.95</v>
-      </c>
+        <v>3.49</v>
+      </c>
+      <c r="N160" s="5" t="n"/>
       <c r="O160" s="5" t="n"/>
       <c r="P160" s="5" t="n"/>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Le Ketch</t>
+          <t>Arpus</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Capitaine Alex - Le Ketch X Wills</t>
+          <t>Mango X Pineapple Gose</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
-        <v>47.3</v>
+        <v>44</v>
       </c>
       <c r="D161" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Letland</t>
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
+          <t>Sour - Fruited Gose</t>
         </is>
       </c>
       <c r="G161" s="4" t="n">
-        <v>4.23</v>
+        <v>4.14</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>10.69</v>
+        <v>5.99</v>
       </c>
       <c r="J161" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/le-ketch-capitaine-alex-le-ketch-x-wills</t>
+          <t>https://debiersalon.nl/products/arpus-mango-x-pineapple-gose</t>
         </is>
       </c>
       <c r="K161" s="2" t="n"/>
       <c r="L161" s="7" t="n">
         <v>55.1</v>
       </c>
-      <c r="M161" s="5" t="n"/>
-      <c r="N161" s="5" t="n"/>
+      <c r="M161" s="5" t="n">
+        <v>6.69</v>
+      </c>
+      <c r="N161" s="5" t="n">
+        <v>5.95</v>
+      </c>
       <c r="O161" s="5" t="n"/>
       <c r="P161" s="5" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Bearwood Brewing</t>
-        </is>
-      </c>
-      <c r="B162" s="3" t="inlineStr">
-        <is>
-          <t>Future Rust</t>
+          <t>Le Ketch</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Capitaine Alex - Le Ketch X Wills</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
-        <v>44</v>
+        <v>47.3</v>
       </c>
       <c r="D162" s="2" t="inlineStr">
         <is>
-          <t>Engeland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E162" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="G162" s="4" t="n">
-        <v>4.03</v>
+        <v>4.23</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>191</v>
+        <v>69</v>
       </c>
       <c r="I162" s="5" t="n">
-        <v>8.49</v>
+        <v>10.69</v>
       </c>
       <c r="J162" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/bearwood-brewing-future-rust</t>
+          <t>https://debiersalon.nl/products/le-ketch-capitaine-alex-le-ketch-x-wills</t>
         </is>
       </c>
       <c r="K162" s="2" t="n"/>
@@ -8709,42 +8713,42 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Counterpart Brewing</t>
+          <t>Bearwood Brewing</t>
         </is>
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>Empire (Macadamia Nut)</t>
+          <t>Future Rust</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
-        <v>47.3</v>
+        <v>44</v>
       </c>
       <c r="D163" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Engeland</t>
         </is>
       </c>
       <c r="E163" s="2" t="n">
-        <v>11.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double Pastry</t>
+          <t>IPA - Imperial / Double</t>
         </is>
       </c>
       <c r="G163" s="4" t="n">
-        <v>4.15</v>
+        <v>4.03</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>304</v>
+        <v>191</v>
       </c>
       <c r="I163" s="5" t="n">
-        <v>13.99</v>
+        <v>8.49</v>
       </c>
       <c r="J163" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/counterpart-brewing-empire-macadamia-nut</t>
+          <t>https://debiersalon.nl/products/bearwood-brewing-future-rust</t>
         </is>
       </c>
       <c r="K163" s="2" t="n"/>
@@ -8759,12 +8763,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Badlands Brewing Company</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>#SELECT - CITRA (2026)</t>
+          <t>Counterpart Brewing</t>
+        </is>
+      </c>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>Empire (Macadamia Nut)</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
@@ -8776,30 +8780,30 @@
         </is>
       </c>
       <c r="E164" s="2" t="n">
-        <v>6.5</v>
+        <v>11.9</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
-          <t>IPA</t>
+          <t>Stout - Imperial / Double Pastry</t>
         </is>
       </c>
       <c r="G164" s="4" t="n">
-        <v>4.24</v>
+        <v>4.15</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="I164" s="5" t="n">
-        <v>11.49</v>
+        <v>13.99</v>
       </c>
       <c r="J164" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/badlands-brewing-company-select-citra-2026</t>
+          <t>https://debiersalon.nl/products/counterpart-brewing-empire-macadamia-nut</t>
         </is>
       </c>
       <c r="K164" s="2" t="n"/>
       <c r="L164" s="7" t="n">
-        <v>55</v>
+        <v>55.1</v>
       </c>
       <c r="M164" s="5" t="n"/>
       <c r="N164" s="5" t="n"/>
@@ -8809,51 +8813,49 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Azvex Brewing Company</t>
+          <t>Badlands Brewing Company</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>Tennis Racket Theorem</t>
+          <t>#SELECT - CITRA (2026)</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
-        <v>44</v>
+        <v>47.3</v>
       </c>
       <c r="D165" s="2" t="inlineStr">
         <is>
-          <t>Engeland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E165" s="2" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
+          <t>IPA</t>
         </is>
       </c>
       <c r="G165" s="4" t="n">
-        <v>4.13</v>
+        <v>4.24</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>451</v>
+        <v>309</v>
       </c>
       <c r="I165" s="5" t="n">
-        <v>6.89</v>
+        <v>11.49</v>
       </c>
       <c r="J165" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/azvex-brewing-company-tennis-racket-theorem</t>
+          <t>https://debiersalon.nl/products/badlands-brewing-company-select-citra-2026</t>
         </is>
       </c>
       <c r="K165" s="2" t="n"/>
       <c r="L165" s="7" t="n">
-        <v>54.8</v>
-      </c>
-      <c r="M165" s="5" t="n">
-        <v>7.59</v>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="M165" s="5" t="n"/>
       <c r="N165" s="5" t="n"/>
       <c r="O165" s="5" t="n"/>
       <c r="P165" s="5" t="n"/>
@@ -8861,24 +8863,24 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Other Half Brewing Co.</t>
+          <t>Azvex Brewing Company</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>Dollar Slice</t>
+          <t>Tennis Racket Theorem</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
-        <v>47.3</v>
+        <v>44</v>
       </c>
       <c r="D166" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Engeland</t>
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>7.5</v>
+        <v>6.2</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -8886,24 +8888,26 @@
         </is>
       </c>
       <c r="G166" s="4" t="n">
-        <v>4.12</v>
+        <v>4.13</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>11820</v>
+        <v>451</v>
       </c>
       <c r="I166" s="5" t="n">
-        <v>8.19</v>
+        <v>6.89</v>
       </c>
       <c r="J166" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/other-half-brewing-co-dollar-slice</t>
+          <t>https://debiersalon.nl/products/azvex-brewing-company-tennis-racket-theorem</t>
         </is>
       </c>
       <c r="K166" s="2" t="n"/>
       <c r="L166" s="7" t="n">
         <v>54.8</v>
       </c>
-      <c r="M166" s="5" t="n"/>
+      <c r="M166" s="5" t="n">
+        <v>7.59</v>
+      </c>
       <c r="N166" s="5" t="n"/>
       <c r="O166" s="5" t="n"/>
       <c r="P166" s="5" t="n"/>
@@ -8911,12 +8915,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Bad Bones</t>
+          <t>Other Half Brewing Co.</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>Scar Tissue</t>
+          <t>Dollar Slice</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
@@ -8924,34 +8928,34 @@
       </c>
       <c r="D167" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E167" s="2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="G167" s="4" t="n">
-        <v>4.26</v>
+        <v>4.12</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>256</v>
+        <v>11820</v>
       </c>
       <c r="I167" s="5" t="n">
-        <v>11.99</v>
+        <v>8.19</v>
       </c>
       <c r="J167" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/bad-bones-scar-tissue</t>
+          <t>https://debiersalon.nl/products/other-half-brewing-co-dollar-slice</t>
         </is>
       </c>
       <c r="K167" s="2" t="n"/>
       <c r="L167" s="7" t="n">
-        <v>54.7</v>
+        <v>54.8</v>
       </c>
       <c r="M167" s="5" t="n"/>
       <c r="N167" s="5" t="n"/>
@@ -8961,42 +8965,42 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Omnipollo</t>
-        </is>
-      </c>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t>Barrel Aged Coconut Space Brownie</t>
+          <t>Bad Bones</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Scar Tissue</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
-        <v>33</v>
+        <v>47.3</v>
       </c>
       <c r="D168" s="2" t="inlineStr">
         <is>
-          <t>Zweden</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>12.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double Pastry</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="G168" s="4" t="n">
-        <v>4.32</v>
+        <v>4.26</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>957</v>
+        <v>256</v>
       </c>
       <c r="I168" s="5" t="n">
-        <v>18.49</v>
+        <v>11.99</v>
       </c>
       <c r="J168" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/omnipollo-barrel-aged-coconut-space-brownie</t>
+          <t>https://debiersalon.nl/products/bad-bones-scar-tissue</t>
         </is>
       </c>
       <c r="K168" s="2" t="n"/>
@@ -9006,19 +9010,17 @@
       <c r="M168" s="5" t="n"/>
       <c r="N168" s="5" t="n"/>
       <c r="O168" s="5" t="n"/>
-      <c r="P168" s="5" t="n">
-        <v>18.75</v>
-      </c>
+      <c r="P168" s="5" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Blackout Brewing</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>Twisted Metal - Rye Whiskey BA</t>
+          <t>Omnipollo</t>
+        </is>
+      </c>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>Barrel Aged Coconut Space Brownie</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
@@ -9026,84 +9028,86 @@
       </c>
       <c r="D169" s="2" t="inlineStr">
         <is>
-          <t>Roemenië</t>
+          <t>Zweden</t>
         </is>
       </c>
       <c r="E169" s="2" t="n">
-        <v>12</v>
+        <v>12.3</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
+          <t>Stout - Imperial / Double Pastry</t>
         </is>
       </c>
       <c r="G169" s="4" t="n">
-        <v>4.2</v>
+        <v>4.32</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>391</v>
+        <v>957</v>
       </c>
       <c r="I169" s="5" t="n">
-        <v>9.390000000000001</v>
+        <v>18.49</v>
       </c>
       <c r="J169" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/blackout-brewing-twisted-metal-rye-whiskey-ba</t>
+          <t>https://debiersalon.nl/products/omnipollo-barrel-aged-coconut-space-brownie</t>
         </is>
       </c>
       <c r="K169" s="2" t="n"/>
       <c r="L169" s="7" t="n">
-        <v>54.5</v>
+        <v>54.7</v>
       </c>
       <c r="M169" s="5" t="n"/>
       <c r="N169" s="5" t="n"/>
       <c r="O169" s="5" t="n"/>
-      <c r="P169" s="5" t="n"/>
+      <c r="P169" s="5" t="n">
+        <v>18.75</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Fine Balance Brewing</t>
+          <t>Blackout Brewing</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>Oats &amp; Cream: Select Nelson Sauvin</t>
+          <t>Twisted Metal - Rye Whiskey BA</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>47.3</v>
+        <v>33</v>
       </c>
       <c r="D170" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Roemenië</t>
         </is>
       </c>
       <c r="E170" s="2" t="n">
-        <v>6.5</v>
+        <v>12</v>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
+          <t>Stout - Imperial / Double</t>
         </is>
       </c>
       <c r="G170" s="4" t="n">
-        <v>4.19</v>
+        <v>4.2</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>172</v>
+        <v>391</v>
       </c>
       <c r="I170" s="5" t="n">
-        <v>9.99</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="J170" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/fine-balance-brewing-oats-cream-select-nelson-sauvin</t>
+          <t>https://debiersalon.nl/products/blackout-brewing-twisted-metal-rye-whiskey-ba</t>
         </is>
       </c>
       <c r="K170" s="2" t="n"/>
       <c r="L170" s="7" t="n">
-        <v>54.4</v>
+        <v>54.5</v>
       </c>
       <c r="M170" s="5" t="n"/>
       <c r="N170" s="5" t="n"/>
@@ -9113,42 +9117,42 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Hoppy People</t>
-        </is>
-      </c>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>Extratropical Cyclone (Elmeleven collab)</t>
+          <t>Fine Balance Brewing</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Oats &amp; Cream: Select Nelson Sauvin</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>44</v>
+        <v>47.3</v>
       </c>
       <c r="D171" s="2" t="inlineStr">
         <is>
-          <t>Zwitserland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E171" s="2" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
-          <t>Sour - Smoothie / Pastry</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="G171" s="4" t="n">
-        <v>4</v>
+        <v>4.19</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>1077</v>
+        <v>172</v>
       </c>
       <c r="I171" s="5" t="n">
-        <v>8.890000000000001</v>
+        <v>9.99</v>
       </c>
       <c r="J171" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/hoppy-people-extratropical-cyclone-elmeleven-collab</t>
+          <t>https://debiersalon.nl/products/fine-balance-brewing-oats-cream-select-nelson-sauvin</t>
         </is>
       </c>
       <c r="K171" s="2" t="n"/>
@@ -9163,12 +9167,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>SOMA Beer</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>Froth</t>
+          <t>Hoppy People</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>Extratropical Cyclone (Elmeleven collab)</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
@@ -9176,34 +9180,34 @@
       </c>
       <c r="D172" s="2" t="inlineStr">
         <is>
-          <t>Spanje</t>
+          <t>Zwitserland</t>
         </is>
       </c>
       <c r="E172" s="2" t="n">
-        <v>8</v>
+        <v>5.3</v>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>Sour - Smoothie / Pastry</t>
         </is>
       </c>
       <c r="G172" s="4" t="n">
-        <v>4.13</v>
+        <v>4</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>635</v>
+        <v>1077</v>
       </c>
       <c r="I172" s="5" t="n">
-        <v>7.29</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="J172" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/soma-froth</t>
+          <t>https://debiersalon.nl/products/hoppy-people-extratropical-cyclone-elmeleven-collab</t>
         </is>
       </c>
       <c r="K172" s="2" t="n"/>
       <c r="L172" s="7" t="n">
-        <v>54.3</v>
+        <v>54.4</v>
       </c>
       <c r="M172" s="5" t="n"/>
       <c r="N172" s="5" t="n"/>
@@ -9213,12 +9217,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Azvex Brewing Company</t>
+          <t>SOMA Beer</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>Kami's Lookout</t>
+          <t>Froth</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
@@ -9226,38 +9230,36 @@
       </c>
       <c r="D173" s="2" t="inlineStr">
         <is>
-          <t>Engeland</t>
+          <t>Spanje</t>
         </is>
       </c>
       <c r="E173" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="G173" s="4" t="n">
         <v>4.13</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>359</v>
+        <v>635</v>
       </c>
       <c r="I173" s="5" t="n">
-        <v>7.09</v>
+        <v>7.29</v>
       </c>
       <c r="J173" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/azvex-brewing-company-kamis-lookout</t>
+          <t>https://debiersalon.nl/products/soma-froth</t>
         </is>
       </c>
       <c r="K173" s="2" t="n"/>
       <c r="L173" s="7" t="n">
-        <v>54.1</v>
-      </c>
-      <c r="M173" s="5" t="n">
-        <v>7.99</v>
-      </c>
+        <v>54.3</v>
+      </c>
+      <c r="M173" s="5" t="n"/>
       <c r="N173" s="5" t="n"/>
       <c r="O173" s="5" t="n"/>
       <c r="P173" s="5" t="n"/>
@@ -9265,49 +9267,51 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Clef Brewery</t>
-        </is>
-      </c>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>Potica</t>
+          <t>Azvex Brewing Company</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>Kami's Lookout</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="D174" s="2" t="inlineStr">
         <is>
-          <t>Slovenië</t>
+          <t>Engeland</t>
         </is>
       </c>
       <c r="E174" s="2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double Pastry</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="G174" s="4" t="n">
-        <v>4.11</v>
+        <v>4.13</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>653</v>
+        <v>359</v>
       </c>
       <c r="I174" s="5" t="n">
-        <v>19.49</v>
+        <v>7.09</v>
       </c>
       <c r="J174" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/clef-brewery-potica</t>
+          <t>https://debiersalon.nl/products/azvex-brewing-company-kamis-lookout</t>
         </is>
       </c>
       <c r="K174" s="2" t="n"/>
       <c r="L174" s="7" t="n">
         <v>54.1</v>
       </c>
-      <c r="M174" s="5" t="n"/>
+      <c r="M174" s="5" t="n">
+        <v>7.99</v>
+      </c>
       <c r="N174" s="5" t="n"/>
       <c r="O174" s="5" t="n"/>
       <c r="P174" s="5" t="n"/>
@@ -9315,47 +9319,47 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Other Half Brewing Co.</t>
-        </is>
-      </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>Chicken Legs</t>
+          <t>Clef Brewery</t>
+        </is>
+      </c>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>Potica</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>47.3</v>
+        <v>75</v>
       </c>
       <c r="D175" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Slovenië</t>
         </is>
       </c>
       <c r="E175" s="2" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>Stout - Imperial / Double Pastry</t>
         </is>
       </c>
       <c r="G175" s="4" t="n">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>1788</v>
+        <v>653</v>
       </c>
       <c r="I175" s="5" t="n">
-        <v>8.99</v>
+        <v>19.49</v>
       </c>
       <c r="J175" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/other-half-brewing-co-chicken-legs</t>
+          <t>https://debiersalon.nl/products/clef-brewery-potica</t>
         </is>
       </c>
       <c r="K175" s="2" t="n"/>
       <c r="L175" s="7" t="n">
-        <v>54</v>
+        <v>54.1</v>
       </c>
       <c r="M175" s="5" t="n"/>
       <c r="N175" s="5" t="n"/>
@@ -9365,16 +9369,16 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Goose Island Beer Co.</t>
+          <t>Other Half Brewing Co.</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>Night Cap Cuvee (2026)</t>
+          <t>Chicken Legs</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
-        <v>35.5</v>
+        <v>47.3</v>
       </c>
       <c r="D176" s="2" t="inlineStr">
         <is>
@@ -9382,25 +9386,25 @@
         </is>
       </c>
       <c r="E176" s="2" t="n">
-        <v>15.5</v>
+        <v>8.5</v>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="G176" s="4" t="n">
-        <v>4.34</v>
+        <v>4.14</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>1797</v>
+        <v>1788</v>
       </c>
       <c r="I176" s="5" t="n">
-        <v>14.29</v>
+        <v>8.99</v>
       </c>
       <c r="J176" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/goose-island-beer-co-night-cap-cuvee-2026</t>
+          <t>https://debiersalon.nl/products/other-half-brewing-co-chicken-legs</t>
         </is>
       </c>
       <c r="K176" s="2" t="n"/>
@@ -9415,47 +9419,47 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Le Ketch</t>
+          <t>Goose Island Beer Co.</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>Dock 131 - Citra &amp; Riwaka</t>
+          <t>Night Cap Cuvee (2026)</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>47.3</v>
+        <v>35.5</v>
       </c>
       <c r="D177" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E177" s="2" t="n">
-        <v>6.5</v>
+        <v>15.5</v>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
+          <t>Stout - Imperial / Double</t>
         </is>
       </c>
       <c r="G177" s="4" t="n">
-        <v>4.14</v>
+        <v>4.34</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>261</v>
+        <v>1797</v>
       </c>
       <c r="I177" s="5" t="n">
-        <v>8.02</v>
+        <v>14.29</v>
       </c>
       <c r="J177" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/le-ketch-dock-131-citra-riwaka</t>
+          <t>https://debiersalon.nl/products/goose-island-beer-co-night-cap-cuvee-2026</t>
         </is>
       </c>
       <c r="K177" s="2" t="n"/>
       <c r="L177" s="7" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="M177" s="5" t="n"/>
       <c r="N177" s="5" t="n"/>
@@ -10319,47 +10323,47 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>DankHouse Brewing Company</t>
-        </is>
-      </c>
-      <c r="B195" s="3" t="inlineStr">
-        <is>
-          <t>Mashish W/Peanut Butter, Chocolate, And Marshmallow</t>
+          <t>REX Beer Blending &amp; Bottling</t>
+        </is>
+      </c>
+      <c r="B195" s="2" t="inlineStr">
+        <is>
+          <t>De Bergloper Montanjaren Series</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
-        <v>47.3</v>
+        <v>33</v>
       </c>
       <c r="D195" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Nederland</t>
         </is>
       </c>
       <c r="E195" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double Pastry</t>
+          <t>Stout - Imperial / Double</t>
         </is>
       </c>
       <c r="G195" s="4" t="n">
-        <v>4.01</v>
+        <v>4.28</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>779</v>
+        <v>393</v>
       </c>
       <c r="I195" s="5" t="n">
-        <v>10.69</v>
+        <v>12.75</v>
       </c>
       <c r="J195" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/dankhouse-brewing-company-mashish-w-peanut-butter-chocolate-and-marshmallow</t>
+          <t>https://debiersalon.nl/products/rex-beer-blending-bottling-de-bergloper-montanjaren-series</t>
         </is>
       </c>
       <c r="K195" s="2" t="n"/>
       <c r="L195" s="7" t="n">
-        <v>52</v>
+        <v>52.2</v>
       </c>
       <c r="M195" s="5" t="n"/>
       <c r="N195" s="5" t="n"/>
@@ -10369,47 +10373,47 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Lough Gill Brewery</t>
-        </is>
-      </c>
-      <c r="B196" s="2" t="inlineStr">
-        <is>
-          <t>Emerald Barrel Aged</t>
+          <t>DankHouse Brewing Company</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>Mashish W/Peanut Butter, Chocolate, And Marshmallow</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>33</v>
+        <v>47.3</v>
       </c>
       <c r="D196" s="2" t="inlineStr">
         <is>
-          <t>Ierland</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E196" s="2" t="n">
-        <v>14.4</v>
+        <v>13</v>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
+          <t>Stout - Imperial / Double Pastry</t>
         </is>
       </c>
       <c r="G196" s="4" t="n">
-        <v>4.14</v>
+        <v>4.01</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>502</v>
+        <v>779</v>
       </c>
       <c r="I196" s="5" t="n">
-        <v>7.19</v>
+        <v>10.69</v>
       </c>
       <c r="J196" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/lough-gill-brewery-emerald-barrel-aged</t>
+          <t>https://debiersalon.nl/products/dankhouse-brewing-company-mashish-w-peanut-butter-chocolate-and-marshmallow</t>
         </is>
       </c>
       <c r="K196" s="2" t="n"/>
       <c r="L196" s="7" t="n">
-        <v>51.9</v>
+        <v>52</v>
       </c>
       <c r="M196" s="5" t="n"/>
       <c r="N196" s="5" t="n"/>
@@ -10419,47 +10423,47 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Third Moon Brewing Company</t>
+          <t>Lough Gill Brewery</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>Alliance (WILLS collab)</t>
+          <t>Emerald Barrel Aged</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
-        <v>47.3</v>
+        <v>33</v>
       </c>
       <c r="D197" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Ierland</t>
         </is>
       </c>
       <c r="E197" s="2" t="n">
-        <v>6.5</v>
+        <v>14.4</v>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
+          <t>Stout - Imperial / Double</t>
         </is>
       </c>
       <c r="G197" s="4" t="n">
-        <v>4.16</v>
+        <v>4.14</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>305</v>
+        <v>502</v>
       </c>
       <c r="I197" s="5" t="n">
-        <v>9.99</v>
+        <v>7.19</v>
       </c>
       <c r="J197" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/third-moon-brewing-company-alliance-wills-collab</t>
+          <t>https://debiersalon.nl/products/lough-gill-brewery-emerald-barrel-aged</t>
         </is>
       </c>
       <c r="K197" s="2" t="n"/>
       <c r="L197" s="7" t="n">
-        <v>51.8</v>
+        <v>51.9</v>
       </c>
       <c r="M197" s="5" t="n"/>
       <c r="N197" s="5" t="n"/>
@@ -10469,42 +10473,42 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Arpus</t>
+          <t>Third Moon Brewing Company</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>Cherry Fruited Gose</t>
+          <t>Alliance (WILLS collab)</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>44</v>
+        <v>47.3</v>
       </c>
       <c r="D198" s="2" t="inlineStr">
         <is>
-          <t>Letland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E198" s="2" t="n">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
-          <t>Sour - Fruited Gose</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="G198" s="4" t="n">
-        <v>4.05</v>
+        <v>4.16</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>684</v>
+        <v>305</v>
       </c>
       <c r="I198" s="5" t="n">
-        <v>5.79</v>
+        <v>9.99</v>
       </c>
       <c r="J198" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/arpus-cherry-fruited-gose</t>
+          <t>https://debiersalon.nl/products/third-moon-brewing-company-alliance-wills-collab</t>
         </is>
       </c>
       <c r="K198" s="2" t="n"/>
@@ -10512,102 +10516,102 @@
         <v>51.8</v>
       </c>
       <c r="M198" s="5" t="n"/>
-      <c r="N198" s="5" t="n">
-        <v>5.95</v>
-      </c>
+      <c r="N198" s="5" t="n"/>
       <c r="O198" s="5" t="n"/>
       <c r="P198" s="5" t="n"/>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Popihn</t>
+          <t>Arpus</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>IMPERIAL STOUT</t>
+          <t>Cherry Fruited Gose</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Frankrijk</t>
+          <t>Letland</t>
         </is>
       </c>
       <c r="E199" s="2" t="n">
-        <v>11</v>
+        <v>4.5</v>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
-        </is>
-      </c>
-      <c r="G199" s="2" t="n"/>
-      <c r="H199" s="2" t="n"/>
+          <t>Sour - Fruited Gose</t>
+        </is>
+      </c>
+      <c r="G199" s="4" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="H199" s="2" t="n">
+        <v>684</v>
+      </c>
       <c r="I199" s="5" t="n">
-        <v>5.99</v>
+        <v>5.79</v>
       </c>
       <c r="J199" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/popihn-imperial-stout</t>
+          <t>https://debiersalon.nl/products/arpus-cherry-fruited-gose</t>
         </is>
       </c>
       <c r="K199" s="2" t="n"/>
       <c r="L199" s="7" t="n">
-        <v>51.7</v>
+        <v>51.8</v>
       </c>
       <c r="M199" s="5" t="n"/>
-      <c r="N199" s="5" t="n"/>
+      <c r="N199" s="5" t="n">
+        <v>5.95</v>
+      </c>
       <c r="O199" s="5" t="n"/>
       <c r="P199" s="5" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>BreWskey</t>
+          <t>Popihn</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>MORPHE</t>
+          <t>IMPERIAL STOUT</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>47.3</v>
+        <v>33</v>
       </c>
       <c r="D200" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Frankrijk</t>
         </is>
       </c>
       <c r="E200" s="2" t="n">
-        <v>6.5</v>
+        <v>11</v>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
-        </is>
-      </c>
-      <c r="G200" s="4" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="H200" s="2" t="n">
-        <v>273</v>
-      </c>
+          <t>Stout - Imperial / Double</t>
+        </is>
+      </c>
+      <c r="G200" s="2" t="n"/>
+      <c r="H200" s="2" t="n"/>
       <c r="I200" s="5" t="n">
-        <v>9.99</v>
+        <v>5.99</v>
       </c>
       <c r="J200" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/brewskey-morphe</t>
+          <t>https://debiersalon.nl/products/popihn-imperial-stout</t>
         </is>
       </c>
       <c r="K200" s="2" t="n"/>
       <c r="L200" s="7" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="M200" s="5" t="n"/>
       <c r="N200" s="5" t="n"/>
@@ -10617,12 +10621,12 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>Third Moon Brewing Company</t>
+          <t>BreWskey</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>All Things Die (2026)</t>
+          <t>MORPHE</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
@@ -10634,30 +10638,30 @@
         </is>
       </c>
       <c r="E201" s="2" t="n">
-        <v>8.1</v>
+        <v>6.5</v>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="G201" s="4" t="n">
-        <v>4.21</v>
+        <v>4.16</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>174</v>
+        <v>273</v>
       </c>
       <c r="I201" s="5" t="n">
-        <v>11.49</v>
+        <v>9.99</v>
       </c>
       <c r="J201" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/third-moon-brewing-company-all-things-die-2026</t>
+          <t>https://debiersalon.nl/products/brewskey-morphe</t>
         </is>
       </c>
       <c r="K201" s="2" t="n"/>
       <c r="L201" s="7" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="M201" s="5" t="n"/>
       <c r="N201" s="5" t="n"/>
@@ -10667,12 +10671,12 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Van Ewing</t>
+          <t>Third Moon Brewing Company</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>Flock Together</t>
+          <t>All Things Die (2026)</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
@@ -10680,30 +10684,34 @@
       </c>
       <c r="D202" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E202" s="2" t="n">
-        <v>7</v>
+        <v>8.1</v>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
-        </is>
-      </c>
-      <c r="G202" s="2" t="n"/>
-      <c r="H202" s="2" t="n"/>
+          <t>IPA - Imperial / Double New England / Hazy</t>
+        </is>
+      </c>
+      <c r="G202" s="4" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="H202" s="2" t="n">
+        <v>174</v>
+      </c>
       <c r="I202" s="5" t="n">
-        <v>8.69</v>
+        <v>11.49</v>
       </c>
       <c r="J202" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/van-ewing-flock-together</t>
+          <t>https://debiersalon.nl/products/third-moon-brewing-company-all-things-die-2026</t>
         </is>
       </c>
       <c r="K202" s="2" t="n"/>
       <c r="L202" s="7" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="M202" s="5" t="n"/>
       <c r="N202" s="5" t="n"/>
@@ -10713,12 +10721,12 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Mortalis Brewing Company</t>
-        </is>
-      </c>
-      <c r="B203" s="3" t="inlineStr">
-        <is>
-          <t>Hydra | Banana Pineapple Kiwi</t>
+          <t>Van Ewing</t>
+        </is>
+      </c>
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>Flock Together</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
@@ -10734,30 +10742,24 @@
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
-          <t>Sour - Smoothie / Pastry</t>
-        </is>
-      </c>
-      <c r="G203" s="4" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="H203" s="2" t="n">
-        <v>559</v>
-      </c>
+          <t>IPA - New England / Hazy</t>
+        </is>
+      </c>
+      <c r="G203" s="2" t="n"/>
+      <c r="H203" s="2" t="n"/>
       <c r="I203" s="5" t="n">
-        <v>12.69</v>
+        <v>8.69</v>
       </c>
       <c r="J203" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/mortalis-brewing-company-hydra-banana-pineapple-kiwi</t>
+          <t>https://debiersalon.nl/products/van-ewing-flock-together</t>
         </is>
       </c>
       <c r="K203" s="2" t="n"/>
       <c r="L203" s="7" t="n">
-        <v>51.2</v>
-      </c>
-      <c r="M203" s="5" t="n">
-        <v>13.39</v>
-      </c>
+        <v>51.4</v>
+      </c>
+      <c r="M203" s="5" t="n"/>
       <c r="N203" s="5" t="n"/>
       <c r="O203" s="5" t="n"/>
       <c r="P203" s="5" t="n"/>
@@ -10765,12 +10767,12 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Fine Balance Brewing</t>
-        </is>
-      </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>Byway IPA</t>
+          <t>Mortalis Brewing Company</t>
+        </is>
+      </c>
+      <c r="B204" s="3" t="inlineStr">
+        <is>
+          <t>Hydra | Banana Pineapple Kiwi</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
@@ -10778,36 +10780,38 @@
       </c>
       <c r="D204" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E204" s="2" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
+          <t>Sour - Smoothie / Pastry</t>
         </is>
       </c>
       <c r="G204" s="4" t="n">
-        <v>4.11</v>
+        <v>4.08</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>100</v>
+        <v>559</v>
       </c>
       <c r="I204" s="5" t="n">
-        <v>7.27</v>
+        <v>12.69</v>
       </c>
       <c r="J204" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/fine-balance-brewing-byway-ipa</t>
+          <t>https://debiersalon.nl/products/mortalis-brewing-company-hydra-banana-pineapple-kiwi</t>
         </is>
       </c>
       <c r="K204" s="2" t="n"/>
       <c r="L204" s="7" t="n">
         <v>51.2</v>
       </c>
-      <c r="M204" s="5" t="n"/>
+      <c r="M204" s="5" t="n">
+        <v>13.39</v>
+      </c>
       <c r="N204" s="5" t="n"/>
       <c r="O204" s="5" t="n"/>
       <c r="P204" s="5" t="n"/>
@@ -10815,47 +10819,47 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>REX Beer Blending &amp; Bottling</t>
+          <t>Bad Bones</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>De Bergloper Montanjaren Series</t>
+          <t>On The Mend</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
-        <v>33</v>
+        <v>47.3</v>
       </c>
       <c r="D205" s="2" t="inlineStr">
         <is>
-          <t>Nederland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E205" s="2" t="n">
-        <v>14</v>
+        <v>6.2</v>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="G205" s="4" t="n">
-        <v>4.27</v>
+        <v>4.13</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>483</v>
+        <v>204</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>12.75</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="J205" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/rex-beer-blending-bottling-de-bergloper-montanjaren-series</t>
+          <t>https://debiersalon.nl/products/bad-bones-on-the-mend</t>
         </is>
       </c>
       <c r="K205" s="2" t="n"/>
       <c r="L205" s="7" t="n">
-        <v>51</v>
+        <v>51.2</v>
       </c>
       <c r="M205" s="5" t="n"/>
       <c r="N205" s="5" t="n"/>
@@ -10865,51 +10869,49 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Tempest Brewing Co.</t>
+          <t>Fine Balance Brewing</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>Three Hills</t>
+          <t>Byway IPA</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
-        <v>33</v>
+        <v>47.3</v>
       </c>
       <c r="D206" s="2" t="inlineStr">
         <is>
-          <t>Schotland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E206" s="2" t="n">
-        <v>12.5</v>
+        <v>6.5</v>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="G206" s="4" t="n">
-        <v>4.17</v>
+        <v>4.11</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>378</v>
+        <v>100</v>
       </c>
       <c r="I206" s="5" t="n">
-        <v>8.99</v>
+        <v>7.27</v>
       </c>
       <c r="J206" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/tempest-brewing-co-three-hills</t>
+          <t>https://debiersalon.nl/products/fine-balance-brewing-byway-ipa</t>
         </is>
       </c>
       <c r="K206" s="2" t="n"/>
       <c r="L206" s="7" t="n">
-        <v>50.8</v>
-      </c>
-      <c r="M206" s="5" t="n">
-        <v>9.9</v>
-      </c>
+        <v>51.2</v>
+      </c>
+      <c r="M206" s="5" t="n"/>
       <c r="N206" s="5" t="n"/>
       <c r="O206" s="5" t="n"/>
       <c r="P206" s="5" t="n"/>
@@ -10917,49 +10919,51 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>Fine Balance Brewing</t>
+          <t>Tempest Brewing Co.</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>Clay</t>
+          <t>Three Hills</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
-        <v>47.3</v>
+        <v>33</v>
       </c>
       <c r="D207" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Schotland</t>
         </is>
       </c>
       <c r="E207" s="2" t="n">
-        <v>6.5</v>
+        <v>12.5</v>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
+          <t>Stout - Imperial / Double</t>
         </is>
       </c>
       <c r="G207" s="4" t="n">
-        <v>4.15</v>
+        <v>4.17</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>119</v>
+        <v>378</v>
       </c>
       <c r="I207" s="5" t="n">
-        <v>9.49</v>
+        <v>8.99</v>
       </c>
       <c r="J207" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/fine-balance-brewing-clay</t>
+          <t>https://debiersalon.nl/products/tempest-brewing-co-three-hills</t>
         </is>
       </c>
       <c r="K207" s="2" t="n"/>
       <c r="L207" s="7" t="n">
-        <v>50.7</v>
-      </c>
-      <c r="M207" s="5" t="n"/>
+        <v>50.8</v>
+      </c>
+      <c r="M207" s="5" t="n">
+        <v>9.9</v>
+      </c>
       <c r="N207" s="5" t="n"/>
       <c r="O207" s="5" t="n"/>
       <c r="P207" s="5" t="n"/>
@@ -10967,148 +10971,146 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Blackout Brewing</t>
-        </is>
-      </c>
-      <c r="B208" s="3" t="inlineStr">
-        <is>
-          <t>Bless This Mess Vol 1</t>
+          <t>Fine Balance Brewing</t>
+        </is>
+      </c>
+      <c r="B208" s="2" t="inlineStr">
+        <is>
+          <t>Clay</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
-        <v>33</v>
+        <v>47.3</v>
       </c>
       <c r="D208" s="2" t="inlineStr">
         <is>
-          <t>Roemenië</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E208" s="2" t="n">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double Pastry</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="G208" s="4" t="n">
-        <v>4.18</v>
+        <v>4.15</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="I208" s="5" t="n">
-        <v>12.39</v>
+        <v>9.49</v>
       </c>
       <c r="J208" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/blackout-brewing-bless-this-mess-vol-1</t>
+          <t>https://debiersalon.nl/products/fine-balance-brewing-clay</t>
         </is>
       </c>
       <c r="K208" s="2" t="n"/>
       <c r="L208" s="7" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="M208" s="5" t="n">
-        <v>12.99</v>
-      </c>
+        <v>50.7</v>
+      </c>
+      <c r="M208" s="5" t="n"/>
       <c r="N208" s="5" t="n"/>
       <c r="O208" s="5" t="n"/>
-      <c r="P208" s="5" t="n">
-        <v>12.75</v>
-      </c>
+      <c r="P208" s="5" t="n"/>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Arpus</t>
-        </is>
-      </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>TDH Hand-Selected Nectaron X Riwaka IPA</t>
+          <t>Blackout Brewing</t>
+        </is>
+      </c>
+      <c r="B209" s="3" t="inlineStr">
+        <is>
+          <t>Bless This Mess Vol 1</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D209" s="2" t="inlineStr">
         <is>
-          <t>Letland</t>
+          <t>Roemenië</t>
         </is>
       </c>
       <c r="E209" s="2" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
+          <t>Stout - Imperial / Double Pastry</t>
         </is>
       </c>
       <c r="G209" s="4" t="n">
-        <v>4.05</v>
+        <v>4.18</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>563</v>
+        <v>120</v>
       </c>
       <c r="I209" s="5" t="n">
-        <v>6.29</v>
+        <v>12.39</v>
       </c>
       <c r="J209" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/arpus-tdh-hand-selected-nectaron-x-riwaka-ipa</t>
+          <t>https://debiersalon.nl/products/blackout-brewing-bless-this-mess-vol-1</t>
         </is>
       </c>
       <c r="K209" s="2" t="n"/>
       <c r="L209" s="7" t="n">
-        <v>50.4</v>
-      </c>
-      <c r="M209" s="5" t="n"/>
-      <c r="N209" s="5" t="n">
-        <v>6.5</v>
-      </c>
+        <v>50.6</v>
+      </c>
+      <c r="M209" s="5" t="n">
+        <v>12.99</v>
+      </c>
+      <c r="N209" s="5" t="n"/>
       <c r="O209" s="5" t="n"/>
-      <c r="P209" s="5" t="n"/>
+      <c r="P209" s="5" t="n">
+        <v>12.75</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Autodidact Beer</t>
+          <t>Arpus</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>Acid Hologram</t>
+          <t>TDH Hand-Selected Nectaron X Riwaka IPA</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
-        <v>47.3</v>
+        <v>44</v>
       </c>
       <c r="D210" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Letland</t>
         </is>
       </c>
       <c r="E210" s="2" t="n">
-        <v>8.6</v>
+        <v>7.5</v>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="G210" s="4" t="n">
-        <v>4.24</v>
+        <v>4.05</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>659</v>
+        <v>563</v>
       </c>
       <c r="I210" s="5" t="n">
-        <v>12.99</v>
+        <v>6.29</v>
       </c>
       <c r="J210" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/autodidact-beer-acid-hologram</t>
+          <t>https://debiersalon.nl/products/arpus-tdh-hand-selected-nectaron-x-riwaka-ipa</t>
         </is>
       </c>
       <c r="K210" s="2" t="n"/>
@@ -11116,101 +11118,103 @@
         <v>50.4</v>
       </c>
       <c r="M210" s="5" t="n"/>
-      <c r="N210" s="5" t="n"/>
+      <c r="N210" s="5" t="n">
+        <v>6.5</v>
+      </c>
       <c r="O210" s="5" t="n"/>
-      <c r="P210" s="5" t="n">
-        <v>12.99</v>
-      </c>
+      <c r="P210" s="5" t="n"/>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>Pühaste</t>
+          <t>Autodidact Beer</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Moros - Cognac/Whisky/Islay BA (Silver Series)</t>
+          <t>Acid Hologram</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
-        <v>33</v>
+        <v>47.3</v>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Estland</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E211" s="2" t="n">
-        <v>12.5</v>
+        <v>8.6</v>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="G211" s="4" t="n">
-        <v>4.18</v>
+        <v>4.24</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>974</v>
+        <v>659</v>
       </c>
       <c r="I211" s="5" t="n">
-        <v>9.99</v>
+        <v>12.99</v>
       </c>
       <c r="J211" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/puhaste-moros-cognac-whisky-islay-ba-silver-series</t>
+          <t>https://debiersalon.nl/products/autodidact-beer-acid-hologram</t>
         </is>
       </c>
       <c r="K211" s="2" t="n"/>
       <c r="L211" s="7" t="n">
-        <v>50.3</v>
+        <v>50.4</v>
       </c>
       <c r="M211" s="5" t="n"/>
       <c r="N211" s="5" t="n"/>
       <c r="O211" s="5" t="n"/>
-      <c r="P211" s="5" t="n"/>
+      <c r="P211" s="5" t="n">
+        <v>12.99</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>Bad Bones</t>
+          <t>Pühaste</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>On The Mend</t>
+          <t>Moros - Cognac/Whisky/Islay BA (Silver Series)</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
-        <v>47.3</v>
+        <v>33</v>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Estland</t>
         </is>
       </c>
       <c r="E212" s="2" t="n">
-        <v>6.2</v>
+        <v>12.5</v>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
+          <t>Stout - Imperial / Double</t>
         </is>
       </c>
       <c r="G212" s="4" t="n">
-        <v>4.12</v>
+        <v>4.18</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>253</v>
+        <v>974</v>
       </c>
       <c r="I212" s="5" t="n">
-        <v>8.619999999999999</v>
+        <v>9.99</v>
       </c>
       <c r="J212" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/bad-bones-on-the-mend</t>
+          <t>https://debiersalon.nl/products/puhaste-moros-cognac-whisky-islay-ba-silver-series</t>
         </is>
       </c>
       <c r="K212" s="2" t="n"/>
@@ -11375,47 +11379,47 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>Stigbergets Bryggeri</t>
+          <t>LERVIG</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>EPITHYMIA (One Drop collab)</t>
+          <t>Off the Rack Finnish Rye Whisky 2024 By Rackhouse</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
-        <v>44</v>
+        <v>37.5</v>
       </c>
       <c r="D216" s="2" t="inlineStr">
         <is>
-          <t>Zweden</t>
+          <t>Noorwegen</t>
         </is>
       </c>
       <c r="E216" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>14.7</v>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
-          <t>IPA</t>
+          <t>Stout - Imperial / Double</t>
         </is>
       </c>
       <c r="G216" s="4" t="n">
-        <v>4.03</v>
+        <v>4.5</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>1568</v>
+        <v>542</v>
       </c>
       <c r="I216" s="5" t="n">
-        <v>6.59</v>
+        <v>19.49</v>
       </c>
       <c r="J216" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/stigbergets-bryggeri-epithymia</t>
+          <t>https://debiersalon.nl/products/lervig-off-the-rack-finnish-rye-whisky-2024-by-rackhouse</t>
         </is>
       </c>
       <c r="K216" s="2" t="n"/>
       <c r="L216" s="7" t="n">
-        <v>49.7</v>
+        <v>50.1</v>
       </c>
       <c r="M216" s="5" t="n"/>
       <c r="N216" s="5" t="n"/>
@@ -11425,47 +11429,47 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>Other Half Brewing Co.</t>
+          <t>Stigbergets Bryggeri</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>Taco Trophy</t>
+          <t>EPITHYMIA (One Drop collab)</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
-        <v>47.3</v>
+        <v>44</v>
       </c>
       <c r="D217" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Zweden</t>
         </is>
       </c>
       <c r="E217" s="2" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>IPA</t>
         </is>
       </c>
       <c r="G217" s="4" t="n">
-        <v>4.1</v>
+        <v>4.03</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>1585</v>
+        <v>1568</v>
       </c>
       <c r="I217" s="5" t="n">
-        <v>8.99</v>
+        <v>6.59</v>
       </c>
       <c r="J217" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/other-half-brewing-co-taco-trophy</t>
+          <t>https://debiersalon.nl/products/stigbergets-bryggeri-epithymia</t>
         </is>
       </c>
       <c r="K217" s="2" t="n"/>
       <c r="L217" s="7" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="M217" s="5" t="n"/>
       <c r="N217" s="5" t="n"/>
@@ -11475,12 +11479,12 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Tin Barn Brewing</t>
+          <t>Other Half Brewing Co.</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>Back 40 - Cryo Edition</t>
+          <t>Taco Trophy</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
@@ -11492,7 +11496,7 @@
         </is>
       </c>
       <c r="E218" s="2" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
@@ -11500,17 +11504,17 @@
         </is>
       </c>
       <c r="G218" s="4" t="n">
-        <v>4.19</v>
+        <v>4.1</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>154</v>
+        <v>1585</v>
       </c>
       <c r="I218" s="5" t="n">
-        <v>11.49</v>
+        <v>8.99</v>
       </c>
       <c r="J218" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/tin-barn-brewing-back-40-cryo-edition</t>
+          <t>https://debiersalon.nl/products/other-half-brewing-co-taco-trophy</t>
         </is>
       </c>
       <c r="K218" s="2" t="n"/>
@@ -11525,47 +11529,47 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>Metanoia Brewing</t>
+          <t>Tin Barn Brewing</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>Necuvintele - Chattanooga BA</t>
+          <t>Back 40 - Cryo Edition</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
-        <v>33</v>
+        <v>47.3</v>
       </c>
       <c r="D219" s="2" t="inlineStr">
         <is>
-          <t>Roemenië</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E219" s="2" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="G219" s="4" t="n">
-        <v>4.22</v>
+        <v>4.19</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>55</v>
+        <v>154</v>
       </c>
       <c r="I219" s="5" t="n">
-        <v>10.99</v>
+        <v>11.49</v>
       </c>
       <c r="J219" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/metanoia-brewing-necuvintele-chattanooga-ba</t>
+          <t>https://debiersalon.nl/products/tin-barn-brewing-back-40-cryo-edition</t>
         </is>
       </c>
       <c r="K219" s="2" t="n"/>
       <c r="L219" s="7" t="n">
-        <v>49.2</v>
+        <v>49.5</v>
       </c>
       <c r="M219" s="5" t="n"/>
       <c r="N219" s="5" t="n"/>
@@ -11575,42 +11579,42 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Brasserie Sir John Brewing Co.</t>
+          <t>Metanoia Brewing</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>Rêves Électriques</t>
+          <t>Necuvintele - Chattanooga BA</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
-        <v>47.3</v>
+        <v>33</v>
       </c>
       <c r="D220" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Roemenië</t>
         </is>
       </c>
       <c r="E220" s="2" t="n">
-        <v>6.9</v>
+        <v>12</v>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
+          <t>Stout - Imperial / Double</t>
         </is>
       </c>
       <c r="G220" s="4" t="n">
-        <v>4.06</v>
+        <v>4.22</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>238</v>
+        <v>55</v>
       </c>
       <c r="I220" s="5" t="n">
-        <v>7.12</v>
+        <v>10.99</v>
       </c>
       <c r="J220" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/brasserie-sir-john-brewing-co-reves-electriques</t>
+          <t>https://debiersalon.nl/products/metanoia-brewing-necuvintele-chattanooga-ba</t>
         </is>
       </c>
       <c r="K220" s="2" t="n"/>
@@ -11625,12 +11629,12 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>Tired Hands Brewing Company</t>
+          <t>Brasserie Sir John Brewing Co.</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>Pungetopia</t>
+          <t>Rêves Électriques</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
@@ -11638,34 +11642,34 @@
       </c>
       <c r="D221" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E221" s="2" t="n">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="G221" s="4" t="n">
-        <v>4.21</v>
+        <v>4.06</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>391</v>
+        <v>238</v>
       </c>
       <c r="I221" s="5" t="n">
-        <v>12.49</v>
+        <v>7.12</v>
       </c>
       <c r="J221" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/tired-hands-brewing-company-pungetopia</t>
+          <t>https://debiersalon.nl/products/brasserie-sir-john-brewing-co-reves-electriques</t>
         </is>
       </c>
       <c r="K221" s="2" t="n"/>
       <c r="L221" s="7" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="M221" s="5" t="n"/>
       <c r="N221" s="5" t="n"/>
@@ -11675,47 +11679,47 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Cloudwater Brew Co.</t>
+          <t>Tired Hands Brewing Company</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
         <is>
-          <t>11th Birthday Imperial Stout</t>
+          <t>Pungetopia</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
-        <v>44</v>
+        <v>47.3</v>
       </c>
       <c r="D222" s="2" t="inlineStr">
         <is>
-          <t>Engeland</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E222" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F222" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="G222" s="4" t="n">
-        <v>4.15</v>
+        <v>4.21</v>
       </c>
       <c r="H222" s="2" t="n">
-        <v>1033</v>
+        <v>391</v>
       </c>
       <c r="I222" s="5" t="n">
-        <v>11.49</v>
+        <v>12.49</v>
       </c>
       <c r="J222" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/cloudwater-brew-co-11th-birthday-imperial-stout</t>
+          <t>https://debiersalon.nl/products/tired-hands-brewing-company-pungetopia</t>
         </is>
       </c>
       <c r="K222" s="2" t="n"/>
       <c r="L222" s="7" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="M222" s="5" t="n"/>
       <c r="N222" s="5" t="n"/>
@@ -11725,24 +11729,24 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Revolution Brewing</t>
+          <t>Cloudwater Brew Co.</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
         <is>
-          <t>Dethurana</t>
+          <t>11th Birthday Imperial Stout</t>
         </is>
       </c>
       <c r="C223" s="2" t="n">
-        <v>35.5</v>
+        <v>44</v>
       </c>
       <c r="D223" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Engeland</t>
         </is>
       </c>
       <c r="E223" s="2" t="n">
-        <v>14.1</v>
+        <v>11</v>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
@@ -11750,89 +11754,89 @@
         </is>
       </c>
       <c r="G223" s="4" t="n">
-        <v>4.37</v>
+        <v>4.15</v>
       </c>
       <c r="H223" s="2" t="n">
-        <v>1767</v>
+        <v>1033</v>
       </c>
       <c r="I223" s="5" t="n">
-        <v>16.99</v>
+        <v>11.49</v>
       </c>
       <c r="J223" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/revolution-brewing-dethurana</t>
+          <t>https://debiersalon.nl/products/cloudwater-brew-co-11th-birthday-imperial-stout</t>
         </is>
       </c>
       <c r="K223" s="2" t="n"/>
       <c r="L223" s="7" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="M223" s="5" t="n"/>
       <c r="N223" s="5" t="n"/>
       <c r="O223" s="5" t="n"/>
-      <c r="P223" s="5" t="n">
-        <v>16</v>
-      </c>
+      <c r="P223" s="5" t="n"/>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>The Piggy Brewing Company</t>
+          <t>Revolution Brewing</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
         <is>
-          <t>DécaDance</t>
+          <t>Dethurana</t>
         </is>
       </c>
       <c r="C224" s="2" t="n">
-        <v>44</v>
+        <v>35.5</v>
       </c>
       <c r="D224" s="2" t="inlineStr">
         <is>
-          <t>Frankrijk</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E224" s="2" t="n">
-        <v>8</v>
+        <v>14.1</v>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>Stout - Imperial / Double</t>
         </is>
       </c>
       <c r="G224" s="4" t="n">
-        <v>4.1</v>
+        <v>4.37</v>
       </c>
       <c r="H224" s="2" t="n">
-        <v>28</v>
+        <v>1767</v>
       </c>
       <c r="I224" s="5" t="n">
-        <v>6.69</v>
+        <v>16.99</v>
       </c>
       <c r="J224" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/the-piggy-brewing-company-decadance</t>
+          <t>https://debiersalon.nl/products/revolution-brewing-dethurana</t>
         </is>
       </c>
       <c r="K224" s="2" t="n"/>
       <c r="L224" s="7" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="M224" s="5" t="n"/>
       <c r="N224" s="5" t="n"/>
       <c r="O224" s="5" t="n"/>
-      <c r="P224" s="5" t="n"/>
+      <c r="P224" s="5" t="n">
+        <v>16</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Verdant Brewing Co</t>
+          <t>The Piggy Brewing Company</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>Big Stupid Hazy V2</t>
+          <t>DécaDance</t>
         </is>
       </c>
       <c r="C225" s="2" t="n">
@@ -11840,29 +11844,29 @@
       </c>
       <c r="D225" s="2" t="inlineStr">
         <is>
-          <t>Engeland</t>
+          <t>Frankrijk</t>
         </is>
       </c>
       <c r="E225" s="2" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="F225" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="G225" s="4" t="n">
-        <v>4.08</v>
+        <v>4.1</v>
       </c>
       <c r="H225" s="2" t="n">
-        <v>399</v>
+        <v>28</v>
       </c>
       <c r="I225" s="5" t="n">
-        <v>7.49</v>
+        <v>6.69</v>
       </c>
       <c r="J225" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/verdant-brewing-co-big-stupid-hazy-v2</t>
+          <t>https://debiersalon.nl/products/the-piggy-brewing-company-decadance</t>
         </is>
       </c>
       <c r="K225" s="2" t="n"/>
@@ -11877,42 +11881,42 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Brasserie du Bas-Canada</t>
+          <t>Verdant Brewing Co</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>Soupe Primordiale</t>
+          <t>Big Stupid Hazy V2</t>
         </is>
       </c>
       <c r="C226" s="2" t="n">
-        <v>47.3</v>
+        <v>44</v>
       </c>
       <c r="D226" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Engeland</t>
         </is>
       </c>
       <c r="E226" s="2" t="n">
-        <v>7.5</v>
+        <v>6.8</v>
       </c>
       <c r="F226" s="2" t="inlineStr">
         <is>
-          <t>IPA</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="G226" s="4" t="n">
-        <v>4.14</v>
+        <v>4.08</v>
       </c>
       <c r="H226" s="2" t="n">
-        <v>473</v>
+        <v>399</v>
       </c>
       <c r="I226" s="5" t="n">
-        <v>10.49</v>
+        <v>7.49</v>
       </c>
       <c r="J226" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/brasserie-du-bas-canada-soupe-primordiale</t>
+          <t>https://debiersalon.nl/products/verdant-brewing-co-big-stupid-hazy-v2</t>
         </is>
       </c>
       <c r="K226" s="2" t="n"/>
@@ -11927,146 +11931,144 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Blackout Brewing</t>
-        </is>
-      </c>
-      <c r="B227" s="3" t="inlineStr">
-        <is>
-          <t>Delusions of Grandeur</t>
+          <t>Brasserie du Bas-Canada</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>Soupe Primordiale</t>
         </is>
       </c>
       <c r="C227" s="2" t="n">
-        <v>33</v>
+        <v>47.3</v>
       </c>
       <c r="D227" s="2" t="inlineStr">
         <is>
-          <t>Roemenië</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E227" s="2" t="n">
-        <v>10</v>
+        <v>7.5</v>
       </c>
       <c r="F227" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double Pastry</t>
+          <t>IPA</t>
         </is>
       </c>
       <c r="G227" s="4" t="n">
-        <v>4.11</v>
+        <v>4.14</v>
       </c>
       <c r="H227" s="2" t="n">
-        <v>564</v>
+        <v>473</v>
       </c>
       <c r="I227" s="5" t="n">
         <v>10.49</v>
       </c>
       <c r="J227" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/blackout-brewing-delusions-of-grandeur</t>
+          <t>https://debiersalon.nl/products/brasserie-du-bas-canada-soupe-primordiale</t>
         </is>
       </c>
       <c r="K227" s="2" t="n"/>
       <c r="L227" s="7" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="M227" s="5" t="n"/>
       <c r="N227" s="5" t="n"/>
       <c r="O227" s="5" t="n"/>
-      <c r="P227" s="5" t="n">
-        <v>10.75</v>
-      </c>
+      <c r="P227" s="5" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Folkingebrew</t>
-        </is>
-      </c>
-      <c r="B228" s="2" t="inlineStr">
-        <is>
-          <t>It's About Time</t>
+          <t>Blackout Brewing</t>
+        </is>
+      </c>
+      <c r="B228" s="3" t="inlineStr">
+        <is>
+          <t>Delusions of Grandeur</t>
         </is>
       </c>
       <c r="C228" s="2" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D228" s="2" t="inlineStr">
         <is>
-          <t>Nederland</t>
+          <t>Roemenië</t>
         </is>
       </c>
       <c r="E228" s="2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F228" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>Stout - Imperial / Double Pastry</t>
         </is>
       </c>
       <c r="G228" s="4" t="n">
-        <v>4.05</v>
+        <v>4.11</v>
       </c>
       <c r="H228" s="2" t="n">
-        <v>992</v>
+        <v>564</v>
       </c>
       <c r="I228" s="5" t="n">
-        <v>7.29</v>
+        <v>10.49</v>
       </c>
       <c r="J228" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/folkingebrew-its-about-time</t>
+          <t>https://debiersalon.nl/products/blackout-brewing-delusions-of-grandeur</t>
         </is>
       </c>
       <c r="K228" s="2" t="n"/>
       <c r="L228" s="7" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="M228" s="5" t="n"/>
       <c r="N228" s="5" t="n"/>
       <c r="O228" s="5" t="n"/>
       <c r="P228" s="5" t="n">
-        <v>7.75</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>All My Friends Beer Co.</t>
+          <t>Folkingebrew</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>Oddity</t>
+          <t>It's About Time</t>
         </is>
       </c>
       <c r="C229" s="2" t="n">
-        <v>47.3</v>
+        <v>44</v>
       </c>
       <c r="D229" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Nederland</t>
         </is>
       </c>
       <c r="E229" s="2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F229" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double Milk</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="G229" s="4" t="n">
-        <v>4.12</v>
+        <v>4.05</v>
       </c>
       <c r="H229" s="2" t="n">
-        <v>295</v>
+        <v>992</v>
       </c>
       <c r="I229" s="5" t="n">
-        <v>9.99</v>
+        <v>7.29</v>
       </c>
       <c r="J229" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/all-my-friends-beer-co-oddity</t>
+          <t>https://debiersalon.nl/products/folkingebrew-its-about-time</t>
         </is>
       </c>
       <c r="K229" s="2" t="n"/>
@@ -12076,56 +12078,56 @@
       <c r="M229" s="5" t="n"/>
       <c r="N229" s="5" t="n"/>
       <c r="O229" s="5" t="n"/>
-      <c r="P229" s="5" t="n"/>
+      <c r="P229" s="5" t="n">
+        <v>7.75</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Azvex Brewing Company</t>
+          <t>All My Friends Beer Co.</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>Surfing Snails</t>
+          <t>Oddity</t>
         </is>
       </c>
       <c r="C230" s="2" t="n">
-        <v>44</v>
+        <v>47.3</v>
       </c>
       <c r="D230" s="2" t="inlineStr">
         <is>
-          <t>Engeland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E230" s="2" t="n">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="F230" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
+          <t>Stout - Imperial / Double Milk</t>
         </is>
       </c>
       <c r="G230" s="4" t="n">
-        <v>4.05</v>
+        <v>4.12</v>
       </c>
       <c r="H230" s="2" t="n">
-        <v>397</v>
+        <v>295</v>
       </c>
       <c r="I230" s="5" t="n">
-        <v>6.89</v>
+        <v>9.99</v>
       </c>
       <c r="J230" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/azvex-brewing-company-surfing-snails</t>
+          <t>https://debiersalon.nl/products/all-my-friends-beer-co-oddity</t>
         </is>
       </c>
       <c r="K230" s="2" t="n"/>
       <c r="L230" s="7" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="M230" s="5" t="n">
-        <v>7.59</v>
-      </c>
+        <v>48.6</v>
+      </c>
+      <c r="M230" s="5" t="n"/>
       <c r="N230" s="5" t="n"/>
       <c r="O230" s="5" t="n"/>
       <c r="P230" s="5" t="n"/>
@@ -12133,20 +12135,20 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Le Ketch</t>
+          <t>Azvex Brewing Company</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>Capitaine John - Le Ketch X Nano Cinco</t>
+          <t>Surfing Snails</t>
         </is>
       </c>
       <c r="C231" s="2" t="n">
-        <v>47.3</v>
+        <v>44</v>
       </c>
       <c r="D231" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Engeland</t>
         </is>
       </c>
       <c r="E231" s="2" t="n">
@@ -12158,24 +12160,26 @@
         </is>
       </c>
       <c r="G231" s="4" t="n">
-        <v>4.15</v>
+        <v>4.05</v>
       </c>
       <c r="H231" s="2" t="n">
-        <v>217</v>
+        <v>397</v>
       </c>
       <c r="I231" s="5" t="n">
-        <v>10.69</v>
+        <v>6.89</v>
       </c>
       <c r="J231" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/le-ketch-capitaine-john-le-ketch-x-nano-cinco</t>
+          <t>https://debiersalon.nl/products/azvex-brewing-company-surfing-snails</t>
         </is>
       </c>
       <c r="K231" s="2" t="n"/>
       <c r="L231" s="7" t="n">
-        <v>48.4</v>
-      </c>
-      <c r="M231" s="5" t="n"/>
+        <v>48.5</v>
+      </c>
+      <c r="M231" s="5" t="n">
+        <v>7.59</v>
+      </c>
       <c r="N231" s="5" t="n"/>
       <c r="O231" s="5" t="n"/>
       <c r="P231" s="5" t="n"/>
@@ -12188,7 +12192,7 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>Capitaine Terps - Le Ketch X All My Friends</t>
+          <t>Capitaine John - Le Ketch X Nano Cinco</t>
         </is>
       </c>
       <c r="C232" s="2" t="n">
@@ -12200,25 +12204,25 @@
         </is>
       </c>
       <c r="E232" s="2" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="F232" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="G232" s="4" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="H232" s="2" t="n">
-        <v>296</v>
+        <v>217</v>
       </c>
       <c r="I232" s="5" t="n">
-        <v>11.49</v>
+        <v>10.69</v>
       </c>
       <c r="J232" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/le-ketch-capitaine-terps-le-ketch-x-all-my-friends</t>
+          <t>https://debiersalon.nl/products/le-ketch-capitaine-john-le-ketch-x-nano-cinco</t>
         </is>
       </c>
       <c r="K232" s="2" t="n"/>
@@ -12233,47 +12237,47 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Seven Island Brewery</t>
+          <t>Le Ketch</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>Hellfire Master (Dark Ages Series)</t>
+          <t>Capitaine Terps - Le Ketch X All My Friends</t>
         </is>
       </c>
       <c r="C233" s="2" t="n">
-        <v>44</v>
+        <v>47.3</v>
       </c>
       <c r="D233" s="2" t="inlineStr">
         <is>
-          <t>Griekenland</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E233" s="2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="G233" s="4" t="n">
-        <v>4.12</v>
+        <v>4.17</v>
       </c>
       <c r="H233" s="2" t="n">
-        <v>65</v>
+        <v>296</v>
       </c>
       <c r="I233" s="5" t="n">
-        <v>8.69</v>
+        <v>11.49</v>
       </c>
       <c r="J233" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/seven-island-brewery-hellfire-master-dark-ages-series</t>
+          <t>https://debiersalon.nl/products/le-ketch-capitaine-terps-le-ketch-x-all-my-friends</t>
         </is>
       </c>
       <c r="K233" s="2" t="n"/>
       <c r="L233" s="7" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="M233" s="5" t="n"/>
       <c r="N233" s="5" t="n"/>
@@ -12283,47 +12287,47 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Hudson Valley Brewery</t>
+          <t>Seven Island Brewery</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>Total Internal Reflection MOSAIC</t>
+          <t>Hellfire Master (Dark Ages Series)</t>
         </is>
       </c>
       <c r="C234" s="2" t="n">
-        <v>47.3</v>
+        <v>44</v>
       </c>
       <c r="D234" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Griekenland</t>
         </is>
       </c>
       <c r="E234" s="2" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>IPA</t>
+          <t>Stout - Imperial / Double</t>
         </is>
       </c>
       <c r="G234" s="4" t="n">
-        <v>4.18</v>
+        <v>4.12</v>
       </c>
       <c r="H234" s="2" t="n">
-        <v>410</v>
+        <v>65</v>
       </c>
       <c r="I234" s="5" t="n">
-        <v>11.99</v>
+        <v>8.69</v>
       </c>
       <c r="J234" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/hudson-valley-brewery-total-internal-reflection-mosaic</t>
+          <t>https://debiersalon.nl/products/seven-island-brewery-hellfire-master-dark-ages-series</t>
         </is>
       </c>
       <c r="K234" s="2" t="n"/>
       <c r="L234" s="7" t="n">
-        <v>48.2</v>
+        <v>48.3</v>
       </c>
       <c r="M234" s="5" t="n"/>
       <c r="N234" s="5" t="n"/>
@@ -12333,42 +12337,42 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>Aspro Brews</t>
+          <t>Hudson Valley Brewery</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>New Heroes</t>
+          <t>Total Internal Reflection MOSAIC</t>
         </is>
       </c>
       <c r="C235" s="2" t="n">
-        <v>44</v>
+        <v>47.3</v>
       </c>
       <c r="D235" s="2" t="inlineStr">
         <is>
-          <t>Nederland</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E235" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="F235" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>IPA</t>
         </is>
       </c>
       <c r="G235" s="4" t="n">
-        <v>4.01</v>
+        <v>4.18</v>
       </c>
       <c r="H235" s="2" t="n">
-        <v>922</v>
+        <v>410</v>
       </c>
       <c r="I235" s="5" t="n">
-        <v>6.49</v>
+        <v>11.99</v>
       </c>
       <c r="J235" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/aspro-brews-new-heroes</t>
+          <t>https://debiersalon.nl/products/hudson-valley-brewery-total-internal-reflection-mosaic</t>
         </is>
       </c>
       <c r="K235" s="2" t="n"/>
@@ -12383,24 +12387,24 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Counterpart Brewing</t>
+          <t>Aspro Brews</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>Dream Taker</t>
+          <t>New Heroes</t>
         </is>
       </c>
       <c r="C236" s="2" t="n">
-        <v>47.3</v>
+        <v>44</v>
       </c>
       <c r="D236" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Nederland</t>
         </is>
       </c>
       <c r="E236" s="2" t="n">
-        <v>6.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F236" s="2" t="inlineStr">
         <is>
@@ -12408,22 +12412,22 @@
         </is>
       </c>
       <c r="G236" s="4" t="n">
-        <v>4.16</v>
+        <v>4.01</v>
       </c>
       <c r="H236" s="2" t="n">
-        <v>468</v>
+        <v>922</v>
       </c>
       <c r="I236" s="5" t="n">
-        <v>11.49</v>
+        <v>6.49</v>
       </c>
       <c r="J236" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/counterpart-brewing-dream-taker</t>
+          <t>https://debiersalon.nl/products/aspro-brews-new-heroes</t>
         </is>
       </c>
       <c r="K236" s="2" t="n"/>
       <c r="L236" s="7" t="n">
-        <v>48</v>
+        <v>48.2</v>
       </c>
       <c r="M236" s="5" t="n"/>
       <c r="N236" s="5" t="n"/>
@@ -12433,42 +12437,42 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>LERVIG</t>
+          <t>Counterpart Brewing</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>Off the Rack Finnish Rye Whisky 2024 By Rackhouse</t>
+          <t>Dream Taker</t>
         </is>
       </c>
       <c r="C237" s="2" t="n">
-        <v>37.5</v>
+        <v>47.3</v>
       </c>
       <c r="D237" s="2" t="inlineStr">
         <is>
-          <t>Noorwegen</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E237" s="2" t="n">
-        <v>14.7</v>
+        <v>6.5</v>
       </c>
       <c r="F237" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="G237" s="4" t="n">
-        <v>4.45</v>
+        <v>4.16</v>
       </c>
       <c r="H237" s="2" t="n">
-        <v>1149</v>
+        <v>468</v>
       </c>
       <c r="I237" s="5" t="n">
-        <v>19.49</v>
+        <v>11.49</v>
       </c>
       <c r="J237" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/lervig-off-the-rack-finnish-rye-whisky-2024-by-rackhouse</t>
+          <t>https://debiersalon.nl/products/counterpart-brewing-dream-taker</t>
         </is>
       </c>
       <c r="K237" s="2" t="n"/>
@@ -12765,7 +12769,7 @@
         <v>4.07</v>
       </c>
       <c r="H243" s="2" t="n">
-        <v>1325</v>
+        <v>1304</v>
       </c>
       <c r="I243" s="5" t="n">
         <v>8.99</v>
@@ -20363,12 +20367,12 @@
     <row r="395">
       <c r="A395" s="2" t="inlineStr">
         <is>
-          <t>Equilibrium Brewery</t>
-        </is>
-      </c>
-      <c r="B395" s="3" t="inlineStr">
-        <is>
-          <t>Life After Death Star (Batch 7) 2025</t>
+          <t>Imprint Beer Co.</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>Barrel Aged Written In the Stars</t>
         </is>
       </c>
       <c r="C395" s="2" t="n">
@@ -20380,30 +20384,30 @@
         </is>
       </c>
       <c r="E395" s="2" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="F395" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double Pastry</t>
+          <t>Stout - Imperial / Double Coffee</t>
         </is>
       </c>
       <c r="G395" s="4" t="n">
-        <v>4.25</v>
+        <v>4.47</v>
       </c>
       <c r="H395" s="2" t="n">
-        <v>782</v>
+        <v>870</v>
       </c>
       <c r="I395" s="5" t="n">
-        <v>21.99</v>
+        <v>33.49</v>
       </c>
       <c r="J395" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/equilibrium-brewery-life-after-death-star-batch-7-2025</t>
+          <t>https://debiersalon.nl/products/imprint-beer-co-barrel-aged-written-in-the-stars</t>
         </is>
       </c>
       <c r="K395" s="2" t="n"/>
       <c r="L395" s="7" t="n">
-        <v>27.4</v>
+        <v>27.9</v>
       </c>
       <c r="M395" s="5" t="n"/>
       <c r="N395" s="5" t="n"/>
@@ -20413,12 +20417,12 @@
     <row r="396">
       <c r="A396" s="2" t="inlineStr">
         <is>
-          <t>Imprint Beer Co.</t>
-        </is>
-      </c>
-      <c r="B396" s="2" t="inlineStr">
-        <is>
-          <t>Barrel Aged Written In the Stars</t>
+          <t>Equilibrium Brewery</t>
+        </is>
+      </c>
+      <c r="B396" s="3" t="inlineStr">
+        <is>
+          <t>Life After Death Star (Batch 7) 2025</t>
         </is>
       </c>
       <c r="C396" s="2" t="n">
@@ -20430,30 +20434,30 @@
         </is>
       </c>
       <c r="E396" s="2" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="F396" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double Coffee</t>
+          <t>Stout - Imperial / Double Pastry</t>
         </is>
       </c>
       <c r="G396" s="4" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="H396" s="2" t="n">
-        <v>1109</v>
+        <v>782</v>
       </c>
       <c r="I396" s="5" t="n">
-        <v>33.49</v>
+        <v>21.99</v>
       </c>
       <c r="J396" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/imprint-beer-co-barrel-aged-written-in-the-stars</t>
+          <t>https://debiersalon.nl/products/equilibrium-brewery-life-after-death-star-batch-7-2025</t>
         </is>
       </c>
       <c r="K396" s="2" t="n"/>
       <c r="L396" s="7" t="n">
-        <v>27</v>
+        <v>27.4</v>
       </c>
       <c r="M396" s="5" t="n"/>
       <c r="N396" s="5" t="n"/>
@@ -21131,16 +21135,16 @@
     <row r="410">
       <c r="A410" s="2" t="inlineStr">
         <is>
-          <t>Perennial Artisan Ales</t>
+          <t>The Bruery</t>
         </is>
       </c>
       <c r="B410" s="2" t="inlineStr">
         <is>
-          <t>Thrill of the Chase</t>
+          <t>Gray Monday (2025)</t>
         </is>
       </c>
       <c r="C410" s="2" t="n">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="D410" s="2" t="inlineStr">
         <is>
@@ -21148,7 +21152,7 @@
         </is>
       </c>
       <c r="E410" s="2" t="n">
-        <v>13</v>
+        <v>20.9</v>
       </c>
       <c r="F410" s="2" t="inlineStr">
         <is>
@@ -21156,17 +21160,17 @@
         </is>
       </c>
       <c r="G410" s="4" t="n">
-        <v>4.4</v>
+        <v>4.42</v>
       </c>
       <c r="H410" s="2" t="n">
-        <v>906</v>
+        <v>335</v>
       </c>
       <c r="I410" s="5" t="n">
-        <v>67.48999999999999</v>
+        <v>32.49</v>
       </c>
       <c r="J410" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/perennial-artisan-ales-thrill-of-the-chase</t>
+          <t>https://debiersalon.nl/products/the-bruery-gray-monday-2025</t>
         </is>
       </c>
       <c r="K410" s="2" t="n"/>
@@ -21181,16 +21185,16 @@
     <row r="411">
       <c r="A411" s="2" t="inlineStr">
         <is>
-          <t>Pips Meadery</t>
+          <t>Perennial Artisan Ales</t>
         </is>
       </c>
       <c r="B411" s="2" t="inlineStr">
         <is>
-          <t>Barrel-Aged Amalgamation 2026 (Club)</t>
+          <t>Thrill of the Chase</t>
         </is>
       </c>
       <c r="C411" s="2" t="n">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="D411" s="2" t="inlineStr">
         <is>
@@ -21198,51 +21202,49 @@
         </is>
       </c>
       <c r="E411" s="2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F411" s="2" t="inlineStr">
         <is>
-          <t>Mead - Melomel</t>
+          <t>Stout - Imperial / Double</t>
         </is>
       </c>
       <c r="G411" s="4" t="n">
-        <v>4.46</v>
+        <v>4.4</v>
       </c>
       <c r="H411" s="2" t="n">
-        <v>33</v>
+        <v>906</v>
       </c>
       <c r="I411" s="5" t="n">
-        <v>57.49</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="J411" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/pips-meadery-barrel-aged-amalgamation-2026-club</t>
+          <t>https://debiersalon.nl/products/perennial-artisan-ales-thrill-of-the-chase</t>
         </is>
       </c>
       <c r="K411" s="2" t="n"/>
       <c r="L411" s="7" t="n">
-        <v>23.4</v>
+        <v>23.8</v>
       </c>
       <c r="M411" s="5" t="n"/>
       <c r="N411" s="5" t="n"/>
       <c r="O411" s="5" t="n"/>
-      <c r="P411" s="5" t="n">
-        <v>51.75</v>
-      </c>
+      <c r="P411" s="5" t="n"/>
     </row>
     <row r="412">
       <c r="A412" s="2" t="inlineStr">
         <is>
-          <t>Cellarmaker Brewing Company</t>
+          <t>Pips Meadery</t>
         </is>
       </c>
       <c r="B412" s="2" t="inlineStr">
         <is>
-          <t>Bourbon Blammo! (2024)</t>
+          <t>Barrel-Aged Amalgamation 2026 (Club)</t>
         </is>
       </c>
       <c r="C412" s="2" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="D412" s="2" t="inlineStr">
         <is>
@@ -21250,25 +21252,25 @@
         </is>
       </c>
       <c r="E412" s="2" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="F412" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
+          <t>Mead - Melomel</t>
         </is>
       </c>
       <c r="G412" s="4" t="n">
-        <v>4.42</v>
+        <v>4.46</v>
       </c>
       <c r="H412" s="2" t="n">
-        <v>236</v>
+        <v>33</v>
       </c>
       <c r="I412" s="5" t="n">
-        <v>53.69</v>
+        <v>57.49</v>
       </c>
       <c r="J412" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/cellarmaker-brewing-company-bourbon-blammo-2025</t>
+          <t>https://debiersalon.nl/products/pips-meadery-barrel-aged-amalgamation-2026-club</t>
         </is>
       </c>
       <c r="K412" s="2" t="n"/>
@@ -21279,18 +21281,18 @@
       <c r="N412" s="5" t="n"/>
       <c r="O412" s="5" t="n"/>
       <c r="P412" s="5" t="n">
-        <v>52.5</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="2" t="inlineStr">
         <is>
-          <t>Transient Artisan Ales</t>
+          <t>Cellarmaker Brewing Company</t>
         </is>
       </c>
       <c r="B413" s="2" t="inlineStr">
         <is>
-          <t>Buckley Reserve #2 (2025)</t>
+          <t>Bourbon Blammo! (2024)</t>
         </is>
       </c>
       <c r="C413" s="2" t="n">
@@ -21302,7 +21304,7 @@
         </is>
       </c>
       <c r="E413" s="2" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="F413" s="2" t="inlineStr">
         <is>
@@ -21310,41 +21312,43 @@
         </is>
       </c>
       <c r="G413" s="4" t="n">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="H413" s="2" t="n">
-        <v>309</v>
+        <v>236</v>
       </c>
       <c r="I413" s="5" t="n">
-        <v>35.99</v>
+        <v>53.69</v>
       </c>
       <c r="J413" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/transient-artisan-ales-buckley-reserve-2-2025</t>
+          <t>https://debiersalon.nl/products/cellarmaker-brewing-company-bourbon-blammo-2025</t>
         </is>
       </c>
       <c r="K413" s="2" t="n"/>
       <c r="L413" s="7" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="M413" s="5" t="n"/>
       <c r="N413" s="5" t="n"/>
       <c r="O413" s="5" t="n"/>
-      <c r="P413" s="5" t="n"/>
+      <c r="P413" s="5" t="n">
+        <v>52.5</v>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="2" t="inlineStr">
         <is>
-          <t>The Bruery</t>
+          <t>Transient Artisan Ales</t>
         </is>
       </c>
       <c r="B414" s="2" t="inlineStr">
         <is>
-          <t>Black Tuesday (2025)</t>
+          <t>Buckley Reserve #2 (2025)</t>
         </is>
       </c>
       <c r="C414" s="2" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="D414" s="2" t="inlineStr">
         <is>
@@ -21352,7 +21356,7 @@
         </is>
       </c>
       <c r="E414" s="2" t="n">
-        <v>19.1</v>
+        <v>15.5</v>
       </c>
       <c r="F414" s="2" t="inlineStr">
         <is>
@@ -21360,17 +21364,17 @@
         </is>
       </c>
       <c r="G414" s="4" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
       <c r="H414" s="2" t="n">
-        <v>1341</v>
+        <v>309</v>
       </c>
       <c r="I414" s="5" t="n">
-        <v>32.99</v>
+        <v>35.99</v>
       </c>
       <c r="J414" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/the-bruery-black-tuesday-2025</t>
+          <t>https://debiersalon.nl/products/transient-artisan-ales-buckley-reserve-2-2025</t>
         </is>
       </c>
       <c r="K414" s="2" t="n"/>
@@ -21380,23 +21384,21 @@
       <c r="M414" s="5" t="n"/>
       <c r="N414" s="5" t="n"/>
       <c r="O414" s="5" t="n"/>
-      <c r="P414" s="5" t="n">
-        <v>31.95</v>
-      </c>
+      <c r="P414" s="5" t="n"/>
     </row>
     <row r="415">
       <c r="A415" s="2" t="inlineStr">
         <is>
-          <t>Jackie O’s Brewery</t>
+          <t>The Bruery</t>
         </is>
       </c>
       <c r="B415" s="2" t="inlineStr">
         <is>
-          <t>Barlow (2026)</t>
+          <t>Black Tuesday (2025)</t>
         </is>
       </c>
       <c r="C415" s="2" t="n">
-        <v>35.5</v>
+        <v>37.5</v>
       </c>
       <c r="D415" s="2" t="inlineStr">
         <is>
@@ -21404,7 +21406,7 @@
         </is>
       </c>
       <c r="E415" s="2" t="n">
-        <v>15.7</v>
+        <v>19.1</v>
       </c>
       <c r="F415" s="2" t="inlineStr">
         <is>
@@ -21412,29 +21414,29 @@
         </is>
       </c>
       <c r="G415" s="4" t="n">
-        <v>4.41</v>
+        <v>4.38</v>
       </c>
       <c r="H415" s="2" t="n">
-        <v>256</v>
+        <v>1341</v>
       </c>
       <c r="I415" s="5" t="n">
-        <v>22.99</v>
+        <v>32.99</v>
       </c>
       <c r="J415" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/jackie-o-s-brewery-barlow-2026</t>
+          <t>https://debiersalon.nl/products/the-bruery-black-tuesday-2025</t>
         </is>
       </c>
       <c r="K415" s="2" t="n"/>
       <c r="L415" s="7" t="n">
-        <v>22.9</v>
-      </c>
-      <c r="M415" s="5" t="n">
-        <v>23.99</v>
-      </c>
+        <v>23.1</v>
+      </c>
+      <c r="M415" s="5" t="n"/>
       <c r="N415" s="5" t="n"/>
       <c r="O415" s="5" t="n"/>
-      <c r="P415" s="5" t="n"/>
+      <c r="P415" s="5" t="n">
+        <v>31.95</v>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -21444,7 +21446,7 @@
       </c>
       <c r="B416" s="2" t="inlineStr">
         <is>
-          <t>Double Barrel Temple of Minerva (2025)</t>
+          <t>Barlow (2026)</t>
         </is>
       </c>
       <c r="C416" s="2" t="n">
@@ -21456,7 +21458,7 @@
         </is>
       </c>
       <c r="E416" s="2" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="F416" s="2" t="inlineStr">
         <is>
@@ -21464,43 +21466,43 @@
         </is>
       </c>
       <c r="G416" s="4" t="n">
-        <v>4.39</v>
+        <v>4.41</v>
       </c>
       <c r="H416" s="2" t="n">
-        <v>655</v>
+        <v>256</v>
       </c>
       <c r="I416" s="5" t="n">
-        <v>22.49</v>
+        <v>22.99</v>
       </c>
       <c r="J416" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/jackie-o-s-brewery-double-barrel-temple-of-minerva-2025</t>
+          <t>https://debiersalon.nl/products/jackie-o-s-brewery-barlow-2026</t>
         </is>
       </c>
       <c r="K416" s="2" t="n"/>
       <c r="L416" s="7" t="n">
         <v>22.9</v>
       </c>
-      <c r="M416" s="5" t="n"/>
+      <c r="M416" s="5" t="n">
+        <v>23.99</v>
+      </c>
       <c r="N416" s="5" t="n"/>
       <c r="O416" s="5" t="n"/>
-      <c r="P416" s="5" t="n">
-        <v>23.5</v>
-      </c>
+      <c r="P416" s="5" t="n"/>
     </row>
     <row r="417">
       <c r="A417" s="2" t="inlineStr">
         <is>
-          <t>Pips Meadery</t>
+          <t>Jackie O’s Brewery</t>
         </is>
       </c>
       <c r="B417" s="2" t="inlineStr">
         <is>
-          <t>Barrel-Aged Amalgamation 2026 (Heart)</t>
+          <t>Double Barrel Temple of Minerva (2025)</t>
         </is>
       </c>
       <c r="C417" s="2" t="n">
-        <v>37.5</v>
+        <v>35.5</v>
       </c>
       <c r="D417" s="2" t="inlineStr">
         <is>
@@ -21508,51 +21510,51 @@
         </is>
       </c>
       <c r="E417" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F417" s="2" t="inlineStr">
         <is>
-          <t>Mead - Melomel</t>
+          <t>Stout - Imperial / Double</t>
         </is>
       </c>
       <c r="G417" s="4" t="n">
-        <v>4.45</v>
+        <v>4.39</v>
       </c>
       <c r="H417" s="2" t="n">
-        <v>30</v>
+        <v>655</v>
       </c>
       <c r="I417" s="5" t="n">
-        <v>57.49</v>
+        <v>22.49</v>
       </c>
       <c r="J417" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/pips-meadery-barrel-aged-amalgamation-2026-heart</t>
+          <t>https://debiersalon.nl/products/jackie-o-s-brewery-double-barrel-temple-of-minerva-2025</t>
         </is>
       </c>
       <c r="K417" s="2" t="n"/>
       <c r="L417" s="7" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="M417" s="5" t="n"/>
       <c r="N417" s="5" t="n"/>
       <c r="O417" s="5" t="n"/>
       <c r="P417" s="5" t="n">
-        <v>51.75</v>
+        <v>23.5</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
         <is>
-          <t>Equilibrium Brewery</t>
-        </is>
-      </c>
-      <c r="B418" s="3" t="inlineStr">
-        <is>
-          <t>Sir Isaac Fig Newton</t>
+          <t>Pips Meadery</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>Barrel-Aged Amalgamation 2026 (Heart)</t>
         </is>
       </c>
       <c r="C418" s="2" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="D418" s="2" t="inlineStr">
         <is>
@@ -21560,25 +21562,25 @@
         </is>
       </c>
       <c r="E418" s="2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F418" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double Pastry</t>
+          <t>Mead - Melomel</t>
         </is>
       </c>
       <c r="G418" s="4" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="H418" s="2" t="n">
-        <v>171</v>
+        <v>30</v>
       </c>
       <c r="I418" s="5" t="n">
-        <v>20.99</v>
+        <v>57.49</v>
       </c>
       <c r="J418" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/equilibrium-brewery-sir-isaac-fig-newton</t>
+          <t>https://debiersalon.nl/products/pips-meadery-barrel-aged-amalgamation-2026-heart</t>
         </is>
       </c>
       <c r="K418" s="2" t="n"/>
@@ -21588,17 +21590,19 @@
       <c r="M418" s="5" t="n"/>
       <c r="N418" s="5" t="n"/>
       <c r="O418" s="5" t="n"/>
-      <c r="P418" s="5" t="n"/>
+      <c r="P418" s="5" t="n">
+        <v>51.75</v>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="2" t="inlineStr">
         <is>
-          <t>3 Sons Brewing Co.</t>
+          <t>Equilibrium Brewery</t>
         </is>
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
-          <t>Coconut Daydreams</t>
+          <t>Sir Isaac Fig Newton</t>
         </is>
       </c>
       <c r="C419" s="2" t="n">
@@ -21610,7 +21614,7 @@
         </is>
       </c>
       <c r="E419" s="2" t="n">
-        <v>14.8</v>
+        <v>11</v>
       </c>
       <c r="F419" s="2" t="inlineStr">
         <is>
@@ -21618,22 +21622,22 @@
         </is>
       </c>
       <c r="G419" s="4" t="n">
-        <v>4.18</v>
+        <v>4.2</v>
       </c>
       <c r="H419" s="2" t="n">
-        <v>403</v>
+        <v>171</v>
       </c>
       <c r="I419" s="5" t="n">
-        <v>57.99</v>
+        <v>20.99</v>
       </c>
       <c r="J419" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/3-sons-brewing-co-coconut-daydreams</t>
+          <t>https://debiersalon.nl/products/equilibrium-brewery-sir-isaac-fig-newton</t>
         </is>
       </c>
       <c r="K419" s="2" t="n"/>
       <c r="L419" s="7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
       <c r="M419" s="5" t="n"/>
       <c r="N419" s="5" t="n"/>
@@ -21643,16 +21647,16 @@
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>The Bruery</t>
-        </is>
-      </c>
-      <c r="B420" s="2" t="inlineStr">
-        <is>
-          <t>Gray Monday (2025)</t>
+          <t>3 Sons Brewing Co.</t>
+        </is>
+      </c>
+      <c r="B420" s="3" t="inlineStr">
+        <is>
+          <t>Coconut Daydreams</t>
         </is>
       </c>
       <c r="C420" s="2" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="D420" s="2" t="inlineStr">
         <is>
@@ -21660,30 +21664,30 @@
         </is>
       </c>
       <c r="E420" s="2" t="n">
-        <v>20.9</v>
+        <v>14.8</v>
       </c>
       <c r="F420" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
+          <t>Stout - Imperial / Double Pastry</t>
         </is>
       </c>
       <c r="G420" s="4" t="n">
-        <v>4.39</v>
+        <v>4.18</v>
       </c>
       <c r="H420" s="2" t="n">
-        <v>447</v>
+        <v>403</v>
       </c>
       <c r="I420" s="5" t="n">
-        <v>32.49</v>
+        <v>57.99</v>
       </c>
       <c r="J420" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/the-bruery-gray-monday-2025</t>
+          <t>https://debiersalon.nl/products/3-sons-brewing-co-coconut-daydreams</t>
         </is>
       </c>
       <c r="K420" s="2" t="n"/>
       <c r="L420" s="7" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="M420" s="5" t="n"/>
       <c r="N420" s="5" t="n"/>
@@ -21921,7 +21925,7 @@
         <v>4.37</v>
       </c>
       <c r="H425" s="2" t="n">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="I425" s="5" t="n">
         <v>40.99</v>
@@ -21943,42 +21947,42 @@
     <row r="426">
       <c r="A426" s="2" t="inlineStr">
         <is>
-          <t>Fremont Brewing</t>
+          <t>Badlands Brewing Company</t>
         </is>
       </c>
       <c r="B426" s="2" t="inlineStr">
         <is>
-          <t>The Rusty Nail (2026)</t>
+          <t>#SELECT - BBA Ugandan Vanilla (2026)</t>
         </is>
       </c>
       <c r="C426" s="2" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="D426" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E426" s="2" t="n">
-        <v>15.2</v>
+        <v>11.9</v>
       </c>
       <c r="F426" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double Oatmeal</t>
+          <t>Stout - Imperial / Double</t>
         </is>
       </c>
       <c r="G426" s="4" t="n">
-        <v>4.37</v>
+        <v>4.41</v>
       </c>
       <c r="H426" s="2" t="n">
-        <v>608</v>
+        <v>80</v>
       </c>
       <c r="I426" s="5" t="n">
-        <v>40.99</v>
+        <v>32.99</v>
       </c>
       <c r="J426" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/fremont-brewing-the-rusty-nail-2026</t>
+          <t>https://debiersalon.nl/products/badlands-brewing-company-select-bba-ugandan-vanilla-2026</t>
         </is>
       </c>
       <c r="K426" s="2" t="n"/>
@@ -21993,12 +21997,12 @@
     <row r="427">
       <c r="A427" s="2" t="inlineStr">
         <is>
-          <t>Badlands Brewing Company</t>
+          <t>Timber Ales</t>
         </is>
       </c>
       <c r="B427" s="2" t="inlineStr">
         <is>
-          <t>#SELECT - BBA Ugandan Vanilla (2026)</t>
+          <t>Tapestry of Timber No.2</t>
         </is>
       </c>
       <c r="C427" s="2" t="n">
@@ -22006,11 +22010,11 @@
       </c>
       <c r="D427" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E427" s="2" t="n">
-        <v>11.9</v>
+        <v>12.5</v>
       </c>
       <c r="F427" s="2" t="inlineStr">
         <is>
@@ -22018,22 +22022,22 @@
         </is>
       </c>
       <c r="G427" s="4" t="n">
-        <v>4.41</v>
+        <v>4.38</v>
       </c>
       <c r="H427" s="2" t="n">
-        <v>80</v>
+        <v>292</v>
       </c>
       <c r="I427" s="5" t="n">
-        <v>32.99</v>
+        <v>44.99</v>
       </c>
       <c r="J427" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/badlands-brewing-company-select-bba-ugandan-vanilla-2026</t>
+          <t>https://debiersalon.nl/products/timber-ales-tapestry-of-timber-no-2</t>
         </is>
       </c>
       <c r="K427" s="2" t="n"/>
       <c r="L427" s="7" t="n">
-        <v>21.6</v>
+        <v>21.3</v>
       </c>
       <c r="M427" s="5" t="n"/>
       <c r="N427" s="5" t="n"/>
@@ -22043,16 +22047,16 @@
     <row r="428">
       <c r="A428" s="2" t="inlineStr">
         <is>
-          <t>Timber Ales</t>
+          <t>Jackie O’s Brewery</t>
         </is>
       </c>
       <c r="B428" s="2" t="inlineStr">
         <is>
-          <t>Tapestry of Timber No.2</t>
+          <t>XX Anniversary Blend</t>
         </is>
       </c>
       <c r="C428" s="2" t="n">
-        <v>50</v>
+        <v>35.5</v>
       </c>
       <c r="D428" s="2" t="inlineStr">
         <is>
@@ -22060,30 +22064,30 @@
         </is>
       </c>
       <c r="E428" s="2" t="n">
-        <v>12.5</v>
+        <v>14.8</v>
       </c>
       <c r="F428" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
+          <t>Stout</t>
         </is>
       </c>
       <c r="G428" s="4" t="n">
-        <v>4.38</v>
+        <v>4.36</v>
       </c>
       <c r="H428" s="2" t="n">
-        <v>292</v>
+        <v>577</v>
       </c>
       <c r="I428" s="5" t="n">
-        <v>44.99</v>
+        <v>24.49</v>
       </c>
       <c r="J428" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/timber-ales-tapestry-of-timber-no-2</t>
+          <t>https://debiersalon.nl/products/jackie-o-s-brewery-xx-anniversary-blend</t>
         </is>
       </c>
       <c r="K428" s="2" t="n"/>
       <c r="L428" s="7" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="M428" s="5" t="n"/>
       <c r="N428" s="5" t="n"/>
@@ -22093,47 +22097,47 @@
     <row r="429">
       <c r="A429" s="2" t="inlineStr">
         <is>
-          <t>Jackie O’s Brewery</t>
+          <t>Brasserie du Bas-Canada</t>
         </is>
       </c>
       <c r="B429" s="2" t="inlineStr">
         <is>
-          <t>XX Anniversary Blend</t>
+          <t>Valentia</t>
         </is>
       </c>
       <c r="C429" s="2" t="n">
-        <v>35.5</v>
+        <v>37.5</v>
       </c>
       <c r="D429" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="E429" s="2" t="n">
-        <v>14.8</v>
+        <v>10.5</v>
       </c>
       <c r="F429" s="2" t="inlineStr">
         <is>
-          <t>Stout</t>
+          <t>Stout - Imperial / Double Milk</t>
         </is>
       </c>
       <c r="G429" s="4" t="n">
-        <v>4.36</v>
+        <v>4.37</v>
       </c>
       <c r="H429" s="2" t="n">
-        <v>577</v>
+        <v>322</v>
       </c>
       <c r="I429" s="5" t="n">
-        <v>24.49</v>
+        <v>27.99</v>
       </c>
       <c r="J429" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/jackie-o-s-brewery-xx-anniversary-blend</t>
+          <t>https://debiersalon.nl/products/brasserie-du-bas-canada-valentia</t>
         </is>
       </c>
       <c r="K429" s="2" t="n"/>
       <c r="L429" s="7" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="M429" s="5" t="n"/>
       <c r="N429" s="5" t="n"/>
@@ -22143,66 +22147,68 @@
     <row r="430">
       <c r="A430" s="2" t="inlineStr">
         <is>
-          <t>Brasserie du Bas-Canada</t>
+          <t>Perennial Artisan Ales</t>
         </is>
       </c>
       <c r="B430" s="2" t="inlineStr">
         <is>
-          <t>Valentia</t>
+          <t>Barrel-Aged Sump (2026)</t>
         </is>
       </c>
       <c r="C430" s="2" t="n">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="D430" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E430" s="2" t="n">
-        <v>10.5</v>
+        <v>12.7</v>
       </c>
       <c r="F430" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double Milk</t>
+          <t>Stout - Imperial / Double Coffee</t>
         </is>
       </c>
       <c r="G430" s="4" t="n">
         <v>4.37</v>
       </c>
       <c r="H430" s="2" t="n">
-        <v>322</v>
+        <v>295</v>
       </c>
       <c r="I430" s="5" t="n">
-        <v>27.99</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="J430" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/brasserie-du-bas-canada-valentia</t>
+          <t>https://debiersalon.nl/products/perennial-artisan-ales-barrel-aged-sump-2026</t>
         </is>
       </c>
       <c r="K430" s="2" t="n"/>
       <c r="L430" s="7" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="M430" s="5" t="n"/>
       <c r="N430" s="5" t="n"/>
       <c r="O430" s="5" t="n"/>
-      <c r="P430" s="5" t="n"/>
+      <c r="P430" s="5" t="n">
+        <v>62.5</v>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="2" t="inlineStr">
         <is>
-          <t>Perennial Artisan Ales</t>
+          <t>The Bruery</t>
         </is>
       </c>
       <c r="B431" s="2" t="inlineStr">
         <is>
-          <t>Barrel-Aged Sump (2026)</t>
+          <t>Black Tuesday (2024)</t>
         </is>
       </c>
       <c r="C431" s="2" t="n">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="D431" s="2" t="inlineStr">
         <is>
@@ -22210,25 +22216,25 @@
         </is>
       </c>
       <c r="E431" s="2" t="n">
-        <v>12.7</v>
+        <v>19.7</v>
       </c>
       <c r="F431" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double Coffee</t>
+          <t>Stout - Imperial / Double</t>
         </is>
       </c>
       <c r="G431" s="4" t="n">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
       <c r="H431" s="2" t="n">
-        <v>295</v>
+        <v>2274</v>
       </c>
       <c r="I431" s="5" t="n">
-        <v>67.98999999999999</v>
+        <v>32.99</v>
       </c>
       <c r="J431" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/perennial-artisan-ales-barrel-aged-sump-2026</t>
+          <t>https://debiersalon.nl/products/the-bruery-black-tuesday-2024</t>
         </is>
       </c>
       <c r="K431" s="2" t="n"/>
@@ -22239,7 +22245,7 @@
       <c r="N431" s="5" t="n"/>
       <c r="O431" s="5" t="n"/>
       <c r="P431" s="5" t="n">
-        <v>62.5</v>
+        <v>31.95</v>
       </c>
     </row>
     <row r="432">
@@ -22250,7 +22256,7 @@
       </c>
       <c r="B432" s="2" t="inlineStr">
         <is>
-          <t>Black Tuesday (2024)</t>
+          <t>Flying High</t>
         </is>
       </c>
       <c r="C432" s="2" t="n">
@@ -22262,7 +22268,7 @@
         </is>
       </c>
       <c r="E432" s="2" t="n">
-        <v>19.7</v>
+        <v>21.3</v>
       </c>
       <c r="F432" s="2" t="inlineStr">
         <is>
@@ -22270,29 +22276,27 @@
         </is>
       </c>
       <c r="G432" s="4" t="n">
-        <v>4.33</v>
+        <v>4.37</v>
       </c>
       <c r="H432" s="2" t="n">
-        <v>2274</v>
+        <v>271</v>
       </c>
       <c r="I432" s="5" t="n">
-        <v>32.99</v>
+        <v>32.49</v>
       </c>
       <c r="J432" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/the-bruery-black-tuesday-2024</t>
+          <t>https://debiersalon.nl/products/the-bruery-flying-high</t>
         </is>
       </c>
       <c r="K432" s="2" t="n"/>
       <c r="L432" s="7" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="M432" s="5" t="n"/>
       <c r="N432" s="5" t="n"/>
       <c r="O432" s="5" t="n"/>
-      <c r="P432" s="5" t="n">
-        <v>31.95</v>
-      </c>
+      <c r="P432" s="5" t="n"/>
     </row>
     <row r="433">
       <c r="A433" s="2" t="inlineStr">
@@ -22397,16 +22401,16 @@
     <row r="435">
       <c r="A435" s="2" t="inlineStr">
         <is>
-          <t>Bottle Logic Brewing</t>
+          <t>Pips Meadery</t>
         </is>
       </c>
       <c r="B435" s="2" t="inlineStr">
         <is>
-          <t>Fundamental Observation (2025)</t>
+          <t>The Turn (TGABA)</t>
         </is>
       </c>
       <c r="C435" s="2" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="D435" s="2" t="inlineStr">
         <is>
@@ -22418,26 +22422,26 @@
       </c>
       <c r="F435" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
+          <t>Mede</t>
         </is>
       </c>
       <c r="G435" s="4" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="H435" s="2" t="n">
-        <v>2515</v>
+        <v>620</v>
       </c>
       <c r="I435" s="5" t="n">
-        <v>40.99</v>
+        <v>47.75</v>
       </c>
       <c r="J435" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/bottle-logic-brewing-fundamental-observation-2025</t>
+          <t>https://debiersalon.nl/products/pips-meadery-the-turn-tgaba</t>
         </is>
       </c>
       <c r="K435" s="2" t="n"/>
       <c r="L435" s="7" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="M435" s="5" t="n"/>
       <c r="N435" s="5" t="n"/>
@@ -22447,16 +22451,16 @@
     <row r="436">
       <c r="A436" s="2" t="inlineStr">
         <is>
-          <t>The Bruery</t>
+          <t>Bottle Logic Brewing</t>
         </is>
       </c>
       <c r="B436" s="2" t="inlineStr">
         <is>
-          <t>Flying High</t>
+          <t>Fundamental Observation (2025)</t>
         </is>
       </c>
       <c r="C436" s="2" t="n">
-        <v>37.5</v>
+        <v>50</v>
       </c>
       <c r="D436" s="2" t="inlineStr">
         <is>
@@ -22464,7 +22468,7 @@
         </is>
       </c>
       <c r="E436" s="2" t="n">
-        <v>21.3</v>
+        <v>14</v>
       </c>
       <c r="F436" s="2" t="inlineStr">
         <is>
@@ -22472,22 +22476,22 @@
         </is>
       </c>
       <c r="G436" s="4" t="n">
-        <v>4.36</v>
+        <v>4.32</v>
       </c>
       <c r="H436" s="2" t="n">
-        <v>321</v>
+        <v>2515</v>
       </c>
       <c r="I436" s="5" t="n">
-        <v>32.49</v>
+        <v>40.99</v>
       </c>
       <c r="J436" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/the-bruery-flying-high</t>
+          <t>https://debiersalon.nl/products/bottle-logic-brewing-fundamental-observation-2025</t>
         </is>
       </c>
       <c r="K436" s="2" t="n"/>
       <c r="L436" s="7" t="n">
-        <v>20.3</v>
+        <v>20.4</v>
       </c>
       <c r="M436" s="5" t="n"/>
       <c r="N436" s="5" t="n"/>
@@ -22647,16 +22651,16 @@
     <row r="440">
       <c r="A440" s="2" t="inlineStr">
         <is>
-          <t>Pips Meadery</t>
+          <t>Perennial Artisan Ales</t>
         </is>
       </c>
       <c r="B440" s="2" t="inlineStr">
         <is>
-          <t>The Turn (TGABA)</t>
+          <t>Bombraxas (2023)</t>
         </is>
       </c>
       <c r="C440" s="2" t="n">
-        <v>37.5</v>
+        <v>75</v>
       </c>
       <c r="D440" s="2" t="inlineStr">
         <is>
@@ -22664,25 +22668,25 @@
         </is>
       </c>
       <c r="E440" s="2" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="F440" s="2" t="inlineStr">
         <is>
-          <t>Mede</t>
+          <t>Stout - Imperial / Double</t>
         </is>
       </c>
       <c r="G440" s="4" t="n">
-        <v>4.34</v>
+        <v>4.3</v>
       </c>
       <c r="H440" s="2" t="n">
-        <v>676</v>
+        <v>4985</v>
       </c>
       <c r="I440" s="5" t="n">
-        <v>47.75</v>
+        <v>33.49</v>
       </c>
       <c r="J440" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/pips-meadery-the-turn-tgaba</t>
+          <t>https://debiersalon.nl/products/perennial-artisan-ales-bombraxas-2023</t>
         </is>
       </c>
       <c r="K440" s="2" t="n"/>
@@ -22697,24 +22701,24 @@
     <row r="441">
       <c r="A441" s="2" t="inlineStr">
         <is>
-          <t>Perennial Artisan Ales</t>
+          <t>Bereta Brewing Co.</t>
         </is>
       </c>
       <c r="B441" s="2" t="inlineStr">
         <is>
-          <t>Bombraxas (2023)</t>
+          <t>Blackwood (Pühaste collab)</t>
         </is>
       </c>
       <c r="C441" s="2" t="n">
-        <v>75</v>
+        <v>37.5</v>
       </c>
       <c r="D441" s="2" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Roemenië</t>
         </is>
       </c>
       <c r="E441" s="2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="F441" s="2" t="inlineStr">
         <is>
@@ -22722,22 +22726,22 @@
         </is>
       </c>
       <c r="G441" s="4" t="n">
-        <v>4.3</v>
+        <v>4.01</v>
       </c>
       <c r="H441" s="2" t="n">
-        <v>4985</v>
+        <v>328</v>
       </c>
       <c r="I441" s="5" t="n">
-        <v>33.49</v>
+        <v>18.99</v>
       </c>
       <c r="J441" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/perennial-artisan-ales-bombraxas-2023</t>
+          <t>https://debiersalon.nl/products/bereta-brewing-co-blackwood-puhaste-collab</t>
         </is>
       </c>
       <c r="K441" s="2" t="n"/>
       <c r="L441" s="7" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="M441" s="5" t="n"/>
       <c r="N441" s="5" t="n"/>
@@ -22747,47 +22751,47 @@
     <row r="442">
       <c r="A442" s="2" t="inlineStr">
         <is>
-          <t>Bereta Brewing Co.</t>
+          <t>Fremont Brewing</t>
         </is>
       </c>
       <c r="B442" s="2" t="inlineStr">
         <is>
-          <t>Blackwood (Pühaste collab)</t>
+          <t>The Rusty Nail (2026)</t>
         </is>
       </c>
       <c r="C442" s="2" t="n">
-        <v>37.5</v>
+        <v>65</v>
       </c>
       <c r="D442" s="2" t="inlineStr">
         <is>
-          <t>Roemenië</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="E442" s="2" t="n">
-        <v>11</v>
+        <v>15.2</v>
       </c>
       <c r="F442" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
+          <t>Stout - Imperial / Double Oatmeal</t>
         </is>
       </c>
       <c r="G442" s="4" t="n">
-        <v>4.01</v>
+        <v>4.37</v>
       </c>
       <c r="H442" s="2" t="n">
-        <v>328</v>
+        <v>121</v>
       </c>
       <c r="I442" s="5" t="n">
-        <v>18.99</v>
+        <v>40.99</v>
       </c>
       <c r="J442" s="6" t="inlineStr">
         <is>
-          <t>https://debiersalon.nl/products/bereta-brewing-co-blackwood-puhaste-collab</t>
+          <t>https://debiersalon.nl/products/fremont-brewing-the-rusty-nail-2026</t>
         </is>
       </c>
       <c r="K442" s="2" t="n"/>
       <c r="L442" s="7" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="M442" s="5" t="n"/>
       <c r="N442" s="5" t="n"/>
@@ -30094,35 +30098,31 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Hoppy People</t>
+          <t>Mad Scientist collab/ Azvex Brewing Company</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Into The Void</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="n">
-        <v>44</v>
-      </c>
+          <t>Everything Is Temporary La</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n"/>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>IPA</t>
+          <t>Sour</t>
         </is>
       </c>
       <c r="F91" s="4" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="G91" s="2" t="n">
-        <v>64</v>
-      </c>
+        <v>4.19</v>
+      </c>
+      <c r="G91" s="2" t="n"/>
       <c r="H91" s="5" t="n">
-        <v>8.789999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>https://www.bierloods22.nl/nl/hoppy-people-into-the-void.html</t>
+          <t>https://www.bierloods22.nl/nl/mad-scientist-collab-azvex-brewing-company-everyth.html</t>
         </is>
       </c>
       <c r="J91" s="7" t="n">
@@ -30136,35 +30136,39 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Mad Scientist collab/ Azvex Brewing Company</t>
+          <t>Hop Hooligans</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Everything Is Temporary La</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="n"/>
+          <t>Kafkaesque</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>50</v>
+      </c>
       <c r="D92" s="2" t="n"/>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Sour</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="F92" s="4" t="n">
-        <v>4.19</v>
-      </c>
-      <c r="G92" s="2" t="n"/>
+        <v>4.06</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>51</v>
+      </c>
       <c r="H92" s="5" t="n">
-        <v>8.99</v>
+        <v>6.99</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
-          <t>https://www.bierloods22.nl/nl/mad-scientist-collab-azvex-brewing-company-everyth.html</t>
+          <t>https://www.bierloods22.nl/nl/hop-hooligans-kafkaesque.html</t>
         </is>
       </c>
       <c r="J92" s="7" t="n">
-        <v>49</v>
+        <v>48.5</v>
       </c>
       <c r="K92" s="5" t="n"/>
       <c r="L92" s="5" t="n"/>
@@ -30174,16 +30178,16 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Hop Hooligans</t>
+          <t>Arpus Brewing Co. Ārpus Brewing Co.</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Kafkaesque</t>
+          <t>TDH Strata X Taiheke IPA</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D93" s="2" t="n"/>
       <c r="E93" s="2" t="inlineStr">
@@ -30192,113 +30196,113 @@
         </is>
       </c>
       <c r="F93" s="4" t="n">
-        <v>4.06</v>
+        <v>4.1</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>6.99</v>
+        <v>6.79</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>https://www.bierloods22.nl/nl/hop-hooligans-kafkaesque.html</t>
+          <t>https://www.bierloods22.nl/nl/arpus-brewing-co-tdh-strata-x-taiheke-ipa.html</t>
         </is>
       </c>
       <c r="J93" s="7" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="K93" s="5" t="n"/>
-      <c r="L93" s="5" t="n"/>
+        <v>48.3</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>5.95</v>
+      </c>
       <c r="M93" s="5" t="n"/>
       <c r="N93" s="5" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Arpus Brewing Co. Ārpus Brewing Co.</t>
+          <t>Tempest Brewing Co.</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>TDH Strata X Taiheke IPA</t>
+          <t>Three Hills</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D94" s="2" t="n"/>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
+          <t>Stout - Imperial / Double</t>
         </is>
       </c>
       <c r="F94" s="4" t="n">
-        <v>4.1</v>
+        <v>4.17</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>23</v>
+        <v>378</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>6.79</v>
+        <v>9.9</v>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>https://www.bierloods22.nl/nl/arpus-brewing-co-tdh-strata-x-taiheke-ipa.html</t>
+          <t>https://www.bierloods22.nl/nl/tempest-brewing-co-three-hills.html</t>
         </is>
       </c>
       <c r="J94" s="7" t="n">
-        <v>48.3</v>
+        <v>47.8</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="L94" s="5" t="n">
-        <v>5.95</v>
-      </c>
+        <v>8.99</v>
+      </c>
+      <c r="L94" s="5" t="n"/>
       <c r="M94" s="5" t="n"/>
       <c r="N94" s="5" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Tempest Brewing Co.</t>
+          <t>Hop Hooligans</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Three Hills</t>
+          <t>Moonlight Sonata</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D95" s="2" t="n"/>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Stout - Imperial / Double</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="F95" s="4" t="n">
-        <v>4.17</v>
+        <v>4.07</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>378</v>
+        <v>130</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>9.9</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>https://www.bierloods22.nl/nl/tempest-brewing-co-three-hills.html</t>
+          <t>https://www.bierloods22.nl/nl/hop-hooligans-moonlight-sonata.html</t>
         </is>
       </c>
       <c r="J95" s="7" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="K95" s="5" t="n">
-        <v>8.99</v>
-      </c>
+        <v>47.4</v>
+      </c>
+      <c r="K95" s="5" t="n"/>
       <c r="L95" s="5" t="n"/>
       <c r="M95" s="5" t="n"/>
       <c r="N95" s="5" t="n"/>
@@ -30306,39 +30310,37 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Hop Hooligans</t>
+          <t>Mortalis Brewing Company</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Moonlight Sonata</t>
+          <t>Hydra | Papaya + Peach + Pineapple</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
-        <v>50</v>
+        <v>47.3</v>
       </c>
       <c r="D96" s="2" t="n"/>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>Sour</t>
         </is>
       </c>
       <c r="F96" s="4" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="G96" s="2" t="n">
-        <v>130</v>
-      </c>
+        <v>4.32</v>
+      </c>
+      <c r="G96" s="2" t="n"/>
       <c r="H96" s="5" t="n">
-        <v>8.289999999999999</v>
+        <v>13.39</v>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>https://www.bierloods22.nl/nl/hop-hooligans-moonlight-sonata.html</t>
+          <t>https://www.bierloods22.nl/nl/mortalis-brewing-company-hydra-papaya-peach-pineap.html</t>
         </is>
       </c>
       <c r="J96" s="7" t="n">
-        <v>47.4</v>
+        <v>46.9</v>
       </c>
       <c r="K96" s="5" t="n"/>
       <c r="L96" s="5" t="n"/>
@@ -30348,39 +30350,43 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Mortalis Brewing Company</t>
+          <t>Azvex Brewing Company</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>Hydra | Papaya + Peach + Pineapple</t>
+          <t>Surfing Snails</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
-        <v>47.3</v>
+        <v>44</v>
       </c>
       <c r="D97" s="2" t="n"/>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Sour</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="F97" s="4" t="n">
-        <v>4.32</v>
-      </c>
-      <c r="G97" s="2" t="n"/>
+        <v>4.05</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>397</v>
+      </c>
       <c r="H97" s="5" t="n">
-        <v>13.39</v>
+        <v>7.59</v>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
-          <t>https://www.bierloods22.nl/nl/mortalis-brewing-company-hydra-papaya-peach-pineap.html</t>
+          <t>https://www.bierloods22.nl/nl/azvex-brewing-company-surfing-snails.html</t>
         </is>
       </c>
       <c r="J97" s="7" t="n">
-        <v>46.9</v>
-      </c>
-      <c r="K97" s="5" t="n"/>
+        <v>46.8</v>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>6.89</v>
+      </c>
       <c r="L97" s="5" t="n"/>
       <c r="M97" s="5" t="n"/>
       <c r="N97" s="5" t="n"/>
@@ -30388,12 +30394,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Azvex Brewing Company</t>
+          <t>Sudden Death Brewing Co.</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Surfing Snails</t>
+          <t>Forest Folly</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
@@ -30402,29 +30408,27 @@
       <c r="D98" s="2" t="n"/>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="F98" s="4" t="n">
-        <v>4.05</v>
+        <v>4.04</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>397</v>
+        <v>433</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>7.59</v>
+        <v>7.49</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
-          <t>https://www.bierloods22.nl/nl/azvex-brewing-company-surfing-snails.html</t>
+          <t>https://www.bierloods22.nl/nl/sudden-death-brewing-co-forest-folly.html</t>
         </is>
       </c>
       <c r="J98" s="7" t="n">
-        <v>46.8</v>
-      </c>
-      <c r="K98" s="5" t="n">
-        <v>6.89</v>
-      </c>
+        <v>46.6</v>
+      </c>
+      <c r="K98" s="5" t="n"/>
       <c r="L98" s="5" t="n"/>
       <c r="M98" s="5" t="n"/>
       <c r="N98" s="5" t="n"/>
@@ -30432,35 +30436,31 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Sudden Death Brewing Co.</t>
+          <t>Wills</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Forest Folly</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="n">
-        <v>44</v>
-      </c>
+          <t>WILLS X ROCK CITY: MONTRÉAL ROCK CITY</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n"/>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>IPA</t>
         </is>
       </c>
       <c r="F99" s="4" t="n">
-        <v>4.04</v>
-      </c>
-      <c r="G99" s="2" t="n">
-        <v>433</v>
-      </c>
+        <v>4.19</v>
+      </c>
+      <c r="G99" s="2" t="n"/>
       <c r="H99" s="5" t="n">
-        <v>7.49</v>
+        <v>9.99</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
-          <t>https://www.bierloods22.nl/nl/sudden-death-brewing-co-forest-folly.html</t>
+          <t>https://www.bierloods22.nl/nl/wills-wills-x-rock-city-montreal-rock-city.html</t>
         </is>
       </c>
       <c r="J99" s="7" t="n">
@@ -30474,12 +30474,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Wills</t>
+          <t>ATELIER VRAI</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>WILLS X ROCK CITY: MONTRÉAL ROCK CITY</t>
+          <t>SELFLOVE WAS MY FIRST ROMANCE | zettelwirtschaft series 2/5</t>
         </is>
       </c>
       <c r="C100" s="2" t="n"/>
@@ -30490,19 +30490,19 @@
         </is>
       </c>
       <c r="F100" s="4" t="n">
-        <v>4.19</v>
+        <v>4.14</v>
       </c>
       <c r="G100" s="2" t="n"/>
       <c r="H100" s="5" t="n">
-        <v>9.99</v>
+        <v>8.19</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>https://www.bierloods22.nl/nl/wills-wills-x-rock-city-montreal-rock-city.html</t>
+          <t>https://www.bierloods22.nl/nl/atelier-vrai-selflove-was-my-first-romance-zettelw.html</t>
         </is>
       </c>
       <c r="J100" s="7" t="n">
-        <v>46.6</v>
+        <v>45.6</v>
       </c>
       <c r="K100" s="5" t="n"/>
       <c r="L100" s="5" t="n"/>
@@ -30512,103 +30512,103 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>ATELIER VRAI</t>
+          <t>Hoppy People</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>SELFLOVE WAS MY FIRST ROMANCE | zettelwirtschaft series 2/5</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="n"/>
+          <t>Brown Paper Bag</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>44</v>
+      </c>
       <c r="D101" s="2" t="n"/>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>IPA</t>
+          <t>IPA - Imperial / Double New England / Hazy</t>
         </is>
       </c>
       <c r="F101" s="4" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="G101" s="2" t="n"/>
+        <v>4.08</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>424</v>
+      </c>
       <c r="H101" s="5" t="n">
-        <v>8.19</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
-          <t>https://www.bierloods22.nl/nl/atelier-vrai-selflove-was-my-first-romance-zettelw.html</t>
+          <t>https://www.bierloods22.nl/nl/hoppy-people-brown-paper-bag.html</t>
         </is>
       </c>
       <c r="J101" s="7" t="n">
-        <v>45.6</v>
-      </c>
-      <c r="K101" s="5" t="n"/>
+        <v>45.5</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>7.99</v>
+      </c>
       <c r="L101" s="5" t="n"/>
       <c r="M101" s="5" t="n"/>
-      <c r="N101" s="5" t="n"/>
+      <c r="N101" s="5" t="n">
+        <v>8.25</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Hoppy People</t>
+          <t>Fuerst Wiacek</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Brown Paper Bag</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="n">
-        <v>44</v>
-      </c>
+          <t>Gone Native</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n"/>
       <c r="D102" s="2" t="n"/>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>IPA - Imperial / Double New England / Hazy</t>
+          <t>IPA</t>
         </is>
       </c>
       <c r="F102" s="4" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="G102" s="2" t="n">
-        <v>424</v>
-      </c>
+        <v>4.1</v>
+      </c>
+      <c r="G102" s="2" t="n"/>
       <c r="H102" s="5" t="n">
-        <v>8.890000000000001</v>
+        <v>6.49</v>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>https://www.bierloods22.nl/nl/hoppy-people-brown-paper-bag.html</t>
+          <t>https://www.bierloods22.nl/nl/fuerst-wiacek-gone-native.html</t>
         </is>
       </c>
       <c r="J102" s="7" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="K102" s="5" t="n">
-        <v>7.99</v>
-      </c>
+        <v>45.4</v>
+      </c>
+      <c r="K102" s="5" t="n"/>
       <c r="L102" s="5" t="n"/>
       <c r="M102" s="5" t="n"/>
-      <c r="N102" s="5" t="n">
-        <v>8.25</v>
-      </c>
+      <c r="N102" s="5" t="n"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Fuerst Wiacek</t>
+          <t>Radical Way Brewing</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Gone Native</t>
+          <t>Inquisition</t>
         </is>
       </c>
       <c r="C103" s="2" t="n"/>
       <c r="D103" s="2" t="n"/>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>IPA</t>
+          <t>Sour</t>
         </is>
       </c>
       <c r="F103" s="4" t="n">
@@ -30620,7 +30620,7 @@
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>https://www.bierloods22.nl/nl/fuerst-wiacek-gone-native.html</t>
+          <t>https://www.bierloods22.nl/nl/radical-way-brewing-inquisition.html</t>
         </is>
       </c>
       <c r="J103" s="7" t="n">
@@ -30634,35 +30634,39 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Radical Way Brewing</t>
+          <t>Hopalaa</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Inquisition</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="n"/>
+          <t>Olicana Dreamscape</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>44</v>
+      </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Sour</t>
+          <t>IPA - New England / Hazy</t>
         </is>
       </c>
       <c r="F104" s="4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="G104" s="2" t="n"/>
+        <v>4.01</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>40</v>
+      </c>
       <c r="H104" s="5" t="n">
-        <v>6.49</v>
+        <v>6.19</v>
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>https://www.bierloods22.nl/nl/radical-way-brewing-inquisition.html</t>
+          <t>https://www.bierloods22.nl/nl/hopalaa-olicana-dreamscape.html</t>
         </is>
       </c>
       <c r="J104" s="7" t="n">
-        <v>45.4</v>
+        <v>45.2</v>
       </c>
       <c r="K104" s="5" t="n"/>
       <c r="L104" s="5" t="n"/>
@@ -30672,123 +30676,121 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Hopalaa</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>Olicana Dreamscape</t>
+          <t>Azvex Brewing Company</t>
+        </is>
+      </c>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>Operation Genome [26.03] - 450 North</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v>44</v>
       </c>
-      <c r="D105" s="2" t="n"/>
+      <c r="D105" s="2" t="n">
+        <v>25</v>
+      </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>IPA - New England / Hazy</t>
+          <t>Sour - Smoothie / Pastry</t>
         </is>
       </c>
       <c r="F105" s="4" t="n">
-        <v>4.01</v>
+        <v>4.09</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>40</v>
+        <v>1354</v>
       </c>
       <c r="H105" s="5" t="n">
-        <v>6.19</v>
+        <v>14.99</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>https://www.bierloods22.nl/nl/hopalaa-olicana-dreamscape.html</t>
+          <t>https://www.bierloods22.nl/nl/azvex-brewing-company-operation-genome-2603-450-no.html</t>
         </is>
       </c>
       <c r="J105" s="7" t="n">
-        <v>45.2</v>
+        <v>45.1</v>
       </c>
       <c r="K105" s="5" t="n"/>
       <c r="L105" s="5" t="n"/>
-      <c r="M105" s="5" t="n"/>
-      <c r="N105" s="5" t="n"/>
+      <c r="M105" s="5" t="n">
+        <v>14.69</v>
+      </c>
+      <c r="N105" s="5" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Azvex Brewing Company</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>Operation Genome [26.03] - 450 North</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="n">
-        <v>44</v>
-      </c>
-      <c r="D106" s="2" t="n">
-        <v>25</v>
-      </c>
+          <t>Pühaste Brewery Pühaste</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>Sublimis Bourbon BA</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n"/>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Sour - Smoothie / Pastry</t>
-        </is>
-      </c>
-      <c r="F106" s="4" t="n">
-        <v>4.09</v>
-      </c>
-      <c r="G106" s="2" t="n">
-        <v>1354</v>
-      </c>
+          <t>Stout</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="n"/>
+      <c r="G106" s="2" t="n"/>
       <c r="H106" s="5" t="n">
-        <v>14.99</v>
+        <v>10.99</v>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
-          <t>https://www.bierloods22.nl/nl/azvex-brewing-company-operation-genome-2603-450-no.html</t>
+          <t>https://www.bierloods22.nl/nl/puehaste-sublimis-bourbon-ba.html</t>
         </is>
       </c>
       <c r="J106" s="7" t="n">
-        <v>45.1</v>
+        <v>44.3</v>
       </c>
       <c r="K106" s="5" t="n"/>
       <c r="L106" s="5" t="n"/>
-      <c r="M106" s="5" t="n">
-        <v>14.69</v>
-      </c>
-      <c r="N106" s="5" t="n">
-        <v>14</v>
-      </c>
+      <c r="M106" s="5" t="n"/>
+      <c r="N106" s="5" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Pühaste Brewery Pühaste</t>
+          <t>Hoppy People</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>Sublimis Bourbon BA</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="n"/>
+          <t>Into The Void</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>44</v>
+      </c>
       <c r="D107" s="2" t="n"/>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Stout</t>
-        </is>
-      </c>
-      <c r="F107" s="2" t="n"/>
+          <t>IPA</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>4.14</v>
+      </c>
       <c r="G107" s="2" t="n"/>
       <c r="H107" s="5" t="n">
-        <v>10.99</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
-          <t>https://www.bierloods22.nl/nl/puehaste-sublimis-bourbon-ba.html</t>
+          <t>https://www.bierloods22.nl/nl/hoppy-people-into-the-void.html</t>
         </is>
       </c>
       <c r="J107" s="7" t="n">
-        <v>44.3</v>
+        <v>44.1</v>
       </c>
       <c r="K107" s="5" t="n"/>
       <c r="L107" s="5" t="n"/>
@@ -33396,7 +33398,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>De Moersleutel Extravagant Dolcita TIPA</t>
+          <t>Arpus Mango X Grape X Pineapple X Banana X Ice Cream Smoothie</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
@@ -33404,26 +33406,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>IPA - Triple</t>
+          <t>Sour - Smoothie / Pastry</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>4.23</v>
+        <v>4.38</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>55</v>
+        <v>133</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="G3" s="6" t="inlineStr">
         <is>
-          <t>https://www.drankgigant.nl/de-moersleutel-extravagant-dolcita-tipa.html</t>
+          <t>https://www.drankgigant.nl/arpus-mango-x-grape-x-pineapple-x-banana-x-ice-cream-smoothie.html</t>
         </is>
       </c>
       <c r="H3" s="2" t="n"/>
       <c r="I3" s="7" t="n">
-        <v>89.8</v>
+        <v>87.5</v>
       </c>
       <c r="J3" s="5" t="n"/>
       <c r="K3" s="5" t="n"/>
@@ -33433,7 +33435,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Arpus Mango X Grape X Pineapple X Banana X Ice Cream Smoothie</t>
+          <t>Arpus Blueberry X Grape X Blackberry X Plum X Pineaple Sour Ale</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
@@ -33445,24 +33447,26 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>4.38</v>
+        <v>4.3</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>133</v>
+        <v>31</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>7.5</v>
+        <v>6.95</v>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>https://www.drankgigant.nl/arpus-mango-x-grape-x-pineapple-x-banana-x-ice-cream-smoothie.html</t>
+          <t>https://www.drankgigant.nl/arpus-blueberry-x-grape-x-blackberry-x-plum-x-pineaple-sour-ale.html</t>
         </is>
       </c>
       <c r="H4" s="2" t="n"/>
       <c r="I4" s="7" t="n">
-        <v>87.5</v>
-      </c>
-      <c r="J4" s="5" t="n"/>
+        <v>82.5</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>7.19</v>
+      </c>
       <c r="K4" s="5" t="n"/>
       <c r="L4" s="5" t="n"/>
       <c r="M4" s="5" t="n"/>
@@ -33470,7 +33474,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Arpus Blueberry X Grape X Blackberry X Plum X Pineaple Sour Ale</t>
+          <t>Arpus X Badlands QDH Mosaic X Citra X Riwaka X Nelson Sauvin</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -33478,30 +33482,28 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Sour - Smoothie / Pastry</t>
+          <t>IPA - Quadruple</t>
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>4.3</v>
+        <v>4.11</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>31</v>
+        <v>2108</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>6.95</v>
+        <v>7.95</v>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>https://www.drankgigant.nl/arpus-blueberry-x-grape-x-blackberry-x-plum-x-pineaple-sour-ale.html</t>
+          <t>https://www.drankgigant.nl/arpus-x-badlands-qdh-mosaic-x-citra-x-riwaka-x-nelson-sauvin.html</t>
         </is>
       </c>
       <c r="H5" s="2" t="n"/>
       <c r="I5" s="7" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>7.19</v>
-      </c>
+        <v>82.40000000000001</v>
+      </c>
+      <c r="J5" s="5" t="n"/>
       <c r="K5" s="5" t="n"/>
       <c r="L5" s="5" t="n"/>
       <c r="M5" s="5" t="n"/>
@@ -33509,7 +33511,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Arpus X Badlands QDH Mosaic X Citra X Riwaka X Nelson Sauvin</t>
+          <t>De Moersleutel Extravagant Dolcita TIPA</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -33517,26 +33519,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>IPA - Quadruple</t>
+          <t>IPA - Triple</t>
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>4.11</v>
+        <v>4.13</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2108</v>
+        <v>418</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>7.95</v>
+        <v>8.5</v>
       </c>
       <c r="G6" s="6" t="inlineStr">
         <is>
-          <t>https://www.drankgigant.nl/arpus-x-badlands-qdh-mosaic-x-citra-x-riwaka-x-nelson-sauvin.html</t>
+          <t>https://www.drankgigant.nl/de-moersleutel-extravagant-dolcita-tipa.html</t>
         </is>
       </c>
       <c r="H6" s="2" t="n"/>
       <c r="I6" s="7" t="n">
-        <v>82.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="J6" s="5" t="n"/>
       <c r="K6" s="5" t="n"/>
@@ -33708,10 +33710,10 @@
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>379</v>
+        <v>3280</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>12.95</v>
@@ -33727,7 +33729,7 @@
         </is>
       </c>
       <c r="I11" s="7" t="n">
-        <v>73.09999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="J11" s="5" t="n">
         <v>13.39</v>
@@ -43366,7 +43368,11 @@
           <t>https://www.hopsandhopes.nl/bieren/barcode-silver-aquamarine-moersleutel-craft-brewery</t>
         </is>
       </c>
-      <c r="K38" s="2" t="n"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>al gehad</t>
+        </is>
+      </c>
       <c r="L38" s="7" t="n">
         <v>74.8</v>
       </c>

--- a/docs/bieroverzicht.xlsx
+++ b/docs/bieroverzicht.xlsx
@@ -33489,7 +33489,7 @@
         <v>4.11</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2108</v>
+        <v>2135</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>7.95</v>
@@ -33602,7 +33602,7 @@
         <v>4.24</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1067</v>
+        <v>1090</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>6.95</v>
@@ -33639,7 +33639,7 @@
         <v>4.24</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1289</v>
+        <v>1296</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>7.5</v>
@@ -33676,7 +33676,7 @@
         <v>4.18</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1368</v>
+        <v>1375</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>6.95</v>
@@ -34013,7 +34013,7 @@
         <v>4.09</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1788</v>
+        <v>1793</v>
       </c>
       <c r="F19" s="5" t="n">
         <v>6.95</v>
@@ -34050,7 +34050,7 @@
         <v>4.04</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>59412</v>
+        <v>59454</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>7.95</v>
